--- a/df_train_transfored.xlsx
+++ b/df_train_transfored.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D679"/>
+  <dimension ref="A1:D678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C13" t="n">
         <v>64.75564682</v>
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="B30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C30" t="n">
         <v>12.68172485</v>
@@ -1337,7 +1337,7 @@
         <v>0</v>
       </c>
       <c r="B65" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C65" t="n">
         <v>96</v>
@@ -1519,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="B78" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C78" t="n">
         <v>38.70225873</v>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="B100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C100" t="n">
         <v>51.94250513</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="B132" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C132" t="n">
         <v>39.72073922</v>
@@ -2499,7 +2499,7 @@
         <v>0</v>
       </c>
       <c r="B148" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C148" t="n">
         <v>11.95893224</v>
@@ -2821,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="B171" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C171" t="n">
         <v>5.092402464</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="B188" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C188" t="n">
         <v>25.33059548</v>
@@ -3451,7 +3451,7 @@
         <v>1</v>
       </c>
       <c r="B216" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C216" t="n">
         <v>2.135523614</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B225" t="n">
         <v>0</v>
       </c>
       <c r="C225" t="n">
-        <v>120.4435318</v>
+        <v>5.650924025</v>
       </c>
       <c r="D225" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="226">
@@ -3591,13 +3591,13 @@
         <v>0</v>
       </c>
       <c r="B226" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C226" t="n">
-        <v>5.782340862</v>
+        <v>81.64271047</v>
       </c>
       <c r="D226" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="227">
@@ -3608,10 +3608,10 @@
         <v>1</v>
       </c>
       <c r="C227" t="n">
-        <v>8.772073922000001</v>
+        <v>138.9404517</v>
       </c>
       <c r="D227" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228">
@@ -3622,10 +3622,10 @@
         <v>0</v>
       </c>
       <c r="C228" t="n">
-        <v>5.650924025</v>
+        <v>32.49281314</v>
       </c>
       <c r="D228" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="229">
@@ -3636,7 +3636,7 @@
         <v>1</v>
       </c>
       <c r="C229" t="n">
-        <v>13.86447639</v>
+        <v>5.815195072</v>
       </c>
       <c r="D229" t="b">
         <v>1</v>
@@ -3647,13 +3647,13 @@
         <v>0</v>
       </c>
       <c r="B230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C230" t="n">
-        <v>81.64271047</v>
+        <v>19.84394251</v>
       </c>
       <c r="D230" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="231">
@@ -3664,10 +3664,10 @@
         <v>1</v>
       </c>
       <c r="C231" t="n">
-        <v>138.9404517</v>
+        <v>6.669404517</v>
       </c>
       <c r="D231" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="232">
@@ -3678,7 +3678,7 @@
         <v>0</v>
       </c>
       <c r="C232" t="n">
-        <v>6.176591376</v>
+        <v>49.31416838</v>
       </c>
       <c r="D232" t="b">
         <v>1</v>
@@ -3692,10 +3692,10 @@
         <v>1</v>
       </c>
       <c r="C233" t="n">
-        <v>7.227926078</v>
+        <v>14.98151951</v>
       </c>
       <c r="D233" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="234">
@@ -3706,7 +3706,7 @@
         <v>1</v>
       </c>
       <c r="C234" t="n">
-        <v>54.07802875</v>
+        <v>16.42710472</v>
       </c>
       <c r="D234" t="b">
         <v>1</v>
@@ -3714,27 +3714,27 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C235" t="n">
-        <v>2.694045175</v>
+        <v>52.73100616</v>
       </c>
       <c r="D235" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C236" t="n">
-        <v>18.33264887</v>
+        <v>27.36755647</v>
       </c>
       <c r="D236" t="b">
         <v>1</v>
@@ -3748,7 +3748,7 @@
         <v>1</v>
       </c>
       <c r="C237" t="n">
-        <v>89.36344969</v>
+        <v>50.98973306</v>
       </c>
       <c r="D237" t="b">
         <v>1</v>
@@ -3756,13 +3756,13 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B238" t="n">
         <v>0</v>
       </c>
       <c r="C238" t="n">
-        <v>48.45995893</v>
+        <v>32.85420945</v>
       </c>
       <c r="D238" t="b">
         <v>1</v>
@@ -3770,30 +3770,30 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B239" t="n">
         <v>0</v>
       </c>
       <c r="C239" t="n">
-        <v>1.18275154</v>
+        <v>70.93223819000001</v>
       </c>
       <c r="D239" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C240" t="n">
-        <v>3.778234086</v>
+        <v>11.49897331</v>
       </c>
       <c r="D240" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="241">
@@ -3804,21 +3804,21 @@
         <v>1</v>
       </c>
       <c r="C241" t="n">
-        <v>76.68172484999999</v>
+        <v>70.83367556</v>
       </c>
       <c r="D241" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C242" t="n">
-        <v>9.790554415000001</v>
+        <v>35.28542094</v>
       </c>
       <c r="D242" t="b">
         <v>1</v>
@@ -3826,13 +3826,13 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B243" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C243" t="n">
-        <v>7.030800821</v>
+        <v>45.30595483</v>
       </c>
       <c r="D243" t="b">
         <v>1</v>
@@ -3840,16 +3840,16 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B244" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C244" t="n">
-        <v>29.96303901</v>
+        <v>23.6550308</v>
       </c>
       <c r="D244" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="245">
@@ -3857,13 +3857,13 @@
         <v>0</v>
       </c>
       <c r="B245" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C245" t="n">
-        <v>23.9835729</v>
+        <v>3.482546201</v>
       </c>
       <c r="D245" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="246">
@@ -3871,10 +3871,10 @@
         <v>0</v>
       </c>
       <c r="B246" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C246" t="n">
-        <v>22.24229979</v>
+        <v>40.3449692</v>
       </c>
       <c r="D246" t="b">
         <v>1</v>
@@ -3882,13 +3882,13 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C247" t="n">
-        <v>10.90759754</v>
+        <v>2.759753593</v>
       </c>
       <c r="D247" t="b">
         <v>1</v>
@@ -3899,13 +3899,13 @@
         <v>0</v>
       </c>
       <c r="B248" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C248" t="n">
-        <v>27.86036961</v>
+        <v>45.30595483</v>
       </c>
       <c r="D248" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="249">
@@ -3916,10 +3916,10 @@
         <v>1</v>
       </c>
       <c r="C249" t="n">
-        <v>2.234086242</v>
+        <v>9.100616016</v>
       </c>
       <c r="D249" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="250">
@@ -3930,10 +3930,10 @@
         <v>1</v>
       </c>
       <c r="C250" t="n">
-        <v>10.11909651</v>
+        <v>11.23613963</v>
       </c>
       <c r="D250" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="251">
@@ -3944,7 +3944,7 @@
         <v>1</v>
       </c>
       <c r="C251" t="n">
-        <v>73.29774127</v>
+        <v>5.848049281</v>
       </c>
       <c r="D251" t="b">
         <v>1</v>
@@ -3958,10 +3958,10 @@
         <v>1</v>
       </c>
       <c r="C252" t="n">
-        <v>24.24640657</v>
+        <v>18.49691992</v>
       </c>
       <c r="D252" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="253">
@@ -3969,10 +3969,10 @@
         <v>0</v>
       </c>
       <c r="B253" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C253" t="n">
-        <v>28.35318275</v>
+        <v>8.410677617999999</v>
       </c>
       <c r="D253" t="b">
         <v>1</v>
@@ -3986,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="C254" t="n">
-        <v>96.65708419000001</v>
+        <v>59.99178645</v>
       </c>
       <c r="D254" t="b">
         <v>0</v>
@@ -3994,16 +3994,16 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C255" t="n">
-        <v>9.790554415000001</v>
+        <v>58.94045175</v>
       </c>
       <c r="D255" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="256">
@@ -4011,10 +4011,10 @@
         <v>0</v>
       </c>
       <c r="B256" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C256" t="n">
-        <v>19.51540041</v>
+        <v>17.11704312</v>
       </c>
       <c r="D256" t="b">
         <v>0</v>
@@ -4025,13 +4025,13 @@
         <v>0</v>
       </c>
       <c r="B257" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C257" t="n">
-        <v>25.23203285</v>
+        <v>81.24845996000001</v>
       </c>
       <c r="D257" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="258">
@@ -4042,24 +4042,24 @@
         <v>1</v>
       </c>
       <c r="C258" t="n">
-        <v>60.94455852</v>
+        <v>50.29979466</v>
       </c>
       <c r="D258" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C259" t="n">
-        <v>59.20328542</v>
+        <v>7.852156057</v>
       </c>
       <c r="D259" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="260">
@@ -4067,10 +4067,10 @@
         <v>0</v>
       </c>
       <c r="B260" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C260" t="n">
-        <v>142.4558522</v>
+        <v>23.9835729</v>
       </c>
       <c r="D260" t="b">
         <v>1</v>
@@ -4078,13 +4078,13 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B261" t="n">
         <v>0</v>
       </c>
       <c r="C261" t="n">
-        <v>23.9835729</v>
+        <v>3.449691992</v>
       </c>
       <c r="D261" t="b">
         <v>1</v>
@@ -4095,13 +4095,13 @@
         <v>0</v>
       </c>
       <c r="B262" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C262" t="n">
-        <v>86.83367556</v>
+        <v>110.0287474</v>
       </c>
       <c r="D262" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="263">
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="B263" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C263" t="n">
-        <v>34.29979466</v>
+        <v>11.53182752</v>
       </c>
       <c r="D263" t="b">
         <v>0</v>
@@ -4126,7 +4126,7 @@
         <v>1</v>
       </c>
       <c r="C264" t="n">
-        <v>23.55646817</v>
+        <v>10.94045175</v>
       </c>
       <c r="D264" t="b">
         <v>1</v>
@@ -4140,10 +4140,10 @@
         <v>1</v>
       </c>
       <c r="C265" t="n">
-        <v>10.51334702</v>
+        <v>3.975359343</v>
       </c>
       <c r="D265" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="266">
@@ -4154,10 +4154,10 @@
         <v>1</v>
       </c>
       <c r="C266" t="n">
-        <v>19.08829569</v>
+        <v>112.788501</v>
       </c>
       <c r="D266" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="267">
@@ -4168,7 +4168,7 @@
         <v>1</v>
       </c>
       <c r="C267" t="n">
-        <v>44.55030801</v>
+        <v>8.772073922000001</v>
       </c>
       <c r="D267" t="b">
         <v>0</v>
@@ -4182,10 +4182,10 @@
         <v>1</v>
       </c>
       <c r="C268" t="n">
-        <v>50.72689938</v>
+        <v>39.88501027</v>
       </c>
       <c r="D268" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="269">
@@ -4193,10 +4193,10 @@
         <v>0</v>
       </c>
       <c r="B269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C269" t="n">
-        <v>47.21149897</v>
+        <v>16.95277207</v>
       </c>
       <c r="D269" t="b">
         <v>0</v>
@@ -4210,10 +4210,10 @@
         <v>1</v>
       </c>
       <c r="C270" t="n">
-        <v>10.51334702</v>
+        <v>3.975359343</v>
       </c>
       <c r="D270" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="271">
@@ -4221,10 +4221,10 @@
         <v>0</v>
       </c>
       <c r="B271" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C271" t="n">
-        <v>90.15195072</v>
+        <v>14.45585216</v>
       </c>
       <c r="D271" t="b">
         <v>0</v>
@@ -4238,10 +4238,10 @@
         <v>1</v>
       </c>
       <c r="C272" t="n">
-        <v>72.41067762</v>
+        <v>32.45995893</v>
       </c>
       <c r="D272" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="273">
@@ -4252,7 +4252,7 @@
         <v>1</v>
       </c>
       <c r="C273" t="n">
-        <v>133.8809035</v>
+        <v>10.7761807</v>
       </c>
       <c r="D273" t="b">
         <v>1</v>
@@ -4266,10 +4266,10 @@
         <v>1</v>
       </c>
       <c r="C274" t="n">
-        <v>94.81724846</v>
+        <v>26.0862423</v>
       </c>
       <c r="D274" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="275">
@@ -4280,7 +4280,7 @@
         <v>1</v>
       </c>
       <c r="C275" t="n">
-        <v>16.62422998</v>
+        <v>144.7556468</v>
       </c>
       <c r="D275" t="b">
         <v>0</v>
@@ -4288,16 +4288,16 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B276" t="n">
         <v>1</v>
       </c>
       <c r="C276" t="n">
-        <v>19.87679671</v>
+        <v>10.02053388</v>
       </c>
       <c r="D276" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="277">
@@ -4305,10 +4305,10 @@
         <v>0</v>
       </c>
       <c r="B277" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C277" t="n">
-        <v>52.79671458</v>
+        <v>123.6960986</v>
       </c>
       <c r="D277" t="b">
         <v>0</v>
@@ -4319,13 +4319,13 @@
         <v>0</v>
       </c>
       <c r="B278" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C278" t="n">
-        <v>30.71868583</v>
+        <v>20.92813142</v>
       </c>
       <c r="D278" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279">
@@ -4336,10 +4336,10 @@
         <v>1</v>
       </c>
       <c r="C279" t="n">
-        <v>16.62422998</v>
+        <v>45.37166324</v>
       </c>
       <c r="D279" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="280">
@@ -4350,10 +4350,10 @@
         <v>1</v>
       </c>
       <c r="C280" t="n">
-        <v>7.030800821</v>
+        <v>8.344969198999999</v>
       </c>
       <c r="D280" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="281">
@@ -4364,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="C281" t="n">
-        <v>17.08418891</v>
+        <v>14.48870637</v>
       </c>
       <c r="D281" t="b">
         <v>0</v>
@@ -4372,13 +4372,13 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C282" t="n">
-        <v>2.825462012</v>
+        <v>33.67556468</v>
       </c>
       <c r="D282" t="b">
         <v>0</v>
@@ -4389,10 +4389,10 @@
         <v>0</v>
       </c>
       <c r="B283" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C283" t="n">
-        <v>38.01232033</v>
+        <v>14.48870637</v>
       </c>
       <c r="D283" t="b">
         <v>0</v>
@@ -4400,16 +4400,16 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B284" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C284" t="n">
-        <v>23.52361396</v>
+        <v>15.14579055</v>
       </c>
       <c r="D284" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="285">
@@ -4417,27 +4417,27 @@
         <v>0</v>
       </c>
       <c r="B285" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C285" t="n">
-        <v>59.76180698</v>
+        <v>33.93839836</v>
       </c>
       <c r="D285" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C286" t="n">
-        <v>42.94045175</v>
+        <v>33.28131417</v>
       </c>
       <c r="D286" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="287">
@@ -4448,10 +4448,10 @@
         <v>1</v>
       </c>
       <c r="C287" t="n">
-        <v>73.29774127</v>
+        <v>16.65708419</v>
       </c>
       <c r="D287" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="288">
@@ -4462,7 +4462,7 @@
         <v>0</v>
       </c>
       <c r="C288" t="n">
-        <v>1.412731006</v>
+        <v>22.73511294</v>
       </c>
       <c r="D288" t="b">
         <v>1</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="B289" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C289" t="n">
-        <v>45.30595483</v>
+        <v>12.8788501</v>
       </c>
       <c r="D289" t="b">
         <v>1</v>
@@ -4487,13 +4487,13 @@
         <v>0</v>
       </c>
       <c r="B290" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C290" t="n">
-        <v>130.9897331</v>
+        <v>27.56468172</v>
       </c>
       <c r="D290" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="291">
@@ -4501,10 +4501,10 @@
         <v>0</v>
       </c>
       <c r="B291" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C291" t="n">
-        <v>29.8973306</v>
+        <v>42.57905544</v>
       </c>
       <c r="D291" t="b">
         <v>0</v>
@@ -4512,27 +4512,27 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B292" t="n">
         <v>0</v>
       </c>
       <c r="C292" t="n">
-        <v>70.93223819000001</v>
+        <v>22.24229979</v>
       </c>
       <c r="D292" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B293" t="n">
         <v>1</v>
       </c>
       <c r="C293" t="n">
-        <v>19.1211499</v>
+        <v>4.501026694</v>
       </c>
       <c r="D293" t="b">
         <v>0</v>
@@ -4546,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="C294" t="n">
-        <v>25.06776181</v>
+        <v>12.78028747</v>
       </c>
       <c r="D294" t="b">
         <v>1</v>
@@ -4557,38 +4557,38 @@
         <v>0</v>
       </c>
       <c r="B295" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C295" t="n">
-        <v>20.46817248</v>
+        <v>79.86858316</v>
       </c>
       <c r="D295" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B296" t="n">
         <v>0</v>
       </c>
       <c r="C296" t="n">
-        <v>16</v>
+        <v>14.06160164</v>
       </c>
       <c r="D296" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C297" t="n">
-        <v>32</v>
+        <v>16.95277207</v>
       </c>
       <c r="D297" t="b">
         <v>0</v>
@@ -4602,10 +4602,10 @@
         <v>1</v>
       </c>
       <c r="C298" t="n">
-        <v>7.852156057</v>
+        <v>5.026694045</v>
       </c>
       <c r="D298" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="299">
@@ -4616,49 +4616,49 @@
         <v>1</v>
       </c>
       <c r="C299" t="n">
-        <v>28.35318275</v>
+        <v>19.74537988</v>
       </c>
       <c r="D299" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C300" t="n">
-        <v>53.81519507</v>
+        <v>48.19712526</v>
       </c>
       <c r="D300" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C301" t="n">
-        <v>49.3798768</v>
+        <v>10.61190965</v>
       </c>
       <c r="D301" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B302" t="n">
         <v>0</v>
       </c>
       <c r="C302" t="n">
-        <v>64.29568789</v>
+        <v>31.96714579</v>
       </c>
       <c r="D302" t="b">
         <v>1</v>
@@ -4669,27 +4669,27 @@
         <v>0</v>
       </c>
       <c r="B303" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C303" t="n">
-        <v>8.082135524</v>
+        <v>132.8952772</v>
       </c>
       <c r="D303" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B304" t="n">
         <v>0</v>
       </c>
       <c r="C304" t="n">
-        <v>61.73305955</v>
+        <v>32.32854209</v>
       </c>
       <c r="D304" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="305">
@@ -4700,35 +4700,35 @@
         <v>1</v>
       </c>
       <c r="C305" t="n">
-        <v>66.69404517</v>
+        <v>26.4476386</v>
       </c>
       <c r="D305" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C306" t="n">
-        <v>24.21355236</v>
+        <v>51.94250513</v>
       </c>
       <c r="D306" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C307" t="n">
-        <v>17.83983573</v>
+        <v>44.97741273</v>
       </c>
       <c r="D307" t="b">
         <v>1</v>
@@ -4742,21 +4742,21 @@
         <v>1</v>
       </c>
       <c r="C308" t="n">
-        <v>9.034907598</v>
+        <v>19.71252567</v>
       </c>
       <c r="D308" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C309" t="n">
-        <v>49.31416838</v>
+        <v>4.073921971</v>
       </c>
       <c r="D309" t="b">
         <v>1</v>
@@ -4764,16 +4764,16 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C310" t="n">
-        <v>11.99178645</v>
+        <v>7.162217659</v>
       </c>
       <c r="D310" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="311">
@@ -4781,13 +4781,13 @@
         <v>0</v>
       </c>
       <c r="B311" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C311" t="n">
-        <v>66.69404517</v>
+        <v>26.21765914</v>
       </c>
       <c r="D311" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="312">
@@ -4795,10 +4795,10 @@
         <v>0</v>
       </c>
       <c r="B312" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C312" t="n">
-        <v>4.533880903</v>
+        <v>11.49897331</v>
       </c>
       <c r="D312" t="b">
         <v>1</v>
@@ -4809,10 +4809,10 @@
         <v>0</v>
       </c>
       <c r="B313" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C313" t="n">
-        <v>3.252566735</v>
+        <v>17.41273101</v>
       </c>
       <c r="D313" t="b">
         <v>1</v>
@@ -4826,7 +4826,7 @@
         <v>1</v>
       </c>
       <c r="C314" t="n">
-        <v>34.59548255</v>
+        <v>16.85420945</v>
       </c>
       <c r="D314" t="b">
         <v>0</v>
@@ -4834,13 +4834,13 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C315" t="n">
-        <v>33.3798768</v>
+        <v>43.92607803</v>
       </c>
       <c r="D315" t="b">
         <v>1</v>
@@ -4848,16 +4848,16 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B316" t="n">
         <v>0</v>
       </c>
       <c r="C316" t="n">
-        <v>3.58110883</v>
+        <v>14.6201232</v>
       </c>
       <c r="D316" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="317">
@@ -4865,27 +4865,27 @@
         <v>0</v>
       </c>
       <c r="B317" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C317" t="n">
-        <v>71.2936345</v>
+        <v>27.23613963</v>
       </c>
       <c r="D317" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B318" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C318" t="n">
-        <v>43.95893224</v>
+        <v>6.176591376</v>
       </c>
       <c r="D318" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="319">
@@ -4893,13 +4893,13 @@
         <v>0</v>
       </c>
       <c r="B319" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C319" t="n">
-        <v>37.09240246</v>
+        <v>11.72895277</v>
       </c>
       <c r="D319" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="320">
@@ -4907,10 +4907,10 @@
         <v>0</v>
       </c>
       <c r="B320" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C320" t="n">
-        <v>34.59548255</v>
+        <v>92.64887064</v>
       </c>
       <c r="D320" t="b">
         <v>0</v>
@@ -4921,10 +4921,10 @@
         <v>0</v>
       </c>
       <c r="B321" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C321" t="n">
-        <v>9.691991786000001</v>
+        <v>132.8952772</v>
       </c>
       <c r="D321" t="b">
         <v>0</v>
@@ -4938,10 +4938,10 @@
         <v>1</v>
       </c>
       <c r="C322" t="n">
-        <v>8.837782341</v>
+        <v>74.05338809</v>
       </c>
       <c r="D322" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="323">
@@ -4952,10 +4952,10 @@
         <v>1</v>
       </c>
       <c r="C323" t="n">
-        <v>50.20123203</v>
+        <v>60.25462012</v>
       </c>
       <c r="D323" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="324">
@@ -4966,21 +4966,21 @@
         <v>1</v>
       </c>
       <c r="C324" t="n">
-        <v>6.603696099</v>
+        <v>34.59548255</v>
       </c>
       <c r="D324" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B325" t="n">
         <v>0</v>
       </c>
       <c r="C325" t="n">
-        <v>9.790554415000001</v>
+        <v>7.030800821</v>
       </c>
       <c r="D325" t="b">
         <v>1</v>
@@ -4994,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="C326" t="n">
-        <v>2.201232033</v>
+        <v>80.98562628000001</v>
       </c>
       <c r="D326" t="b">
         <v>1</v>
@@ -5008,7 +5008,7 @@
         <v>1</v>
       </c>
       <c r="C327" t="n">
-        <v>63.11293634</v>
+        <v>19.58110883</v>
       </c>
       <c r="D327" t="b">
         <v>1</v>
@@ -5016,13 +5016,13 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B328" t="n">
         <v>0</v>
       </c>
       <c r="C328" t="n">
-        <v>22.37371663</v>
+        <v>7.589322382</v>
       </c>
       <c r="D328" t="b">
         <v>1</v>
@@ -5030,16 +5030,16 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C329" t="n">
-        <v>25.65913758</v>
+        <v>93.8973306</v>
       </c>
       <c r="D329" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="330">
@@ -5050,10 +5050,10 @@
         <v>0</v>
       </c>
       <c r="C330" t="n">
-        <v>20.30390144</v>
+        <v>17.01848049</v>
       </c>
       <c r="D330" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="331">
@@ -5064,10 +5064,10 @@
         <v>1</v>
       </c>
       <c r="C331" t="n">
-        <v>7.195071869</v>
+        <v>15.34291581</v>
       </c>
       <c r="D331" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="332">
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="B332" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C332" t="n">
-        <v>11.8275154</v>
+        <v>35.74537988</v>
       </c>
       <c r="D332" t="b">
         <v>1</v>
@@ -5092,7 +5092,7 @@
         <v>1</v>
       </c>
       <c r="C333" t="n">
-        <v>7.589322382</v>
+        <v>3.975359343</v>
       </c>
       <c r="D333" t="b">
         <v>1</v>
@@ -5103,10 +5103,10 @@
         <v>0</v>
       </c>
       <c r="B334" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C334" t="n">
-        <v>123.3347023</v>
+        <v>26.21765914</v>
       </c>
       <c r="D334" t="b">
         <v>1</v>
@@ -5117,13 +5117,13 @@
         <v>0</v>
       </c>
       <c r="B335" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C335" t="n">
-        <v>14.58726899</v>
+        <v>57.62628337</v>
       </c>
       <c r="D335" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="336">
@@ -5134,21 +5134,21 @@
         <v>1</v>
       </c>
       <c r="C336" t="n">
-        <v>163.8110883</v>
+        <v>129.2813142</v>
       </c>
       <c r="D336" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C337" t="n">
-        <v>21.65092402</v>
+        <v>4.993839836</v>
       </c>
       <c r="D337" t="b">
         <v>0</v>
@@ -5156,27 +5156,27 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C338" t="n">
-        <v>15.73716632</v>
+        <v>24.27926078</v>
       </c>
       <c r="D338" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B339" t="n">
         <v>1</v>
       </c>
       <c r="C339" t="n">
-        <v>17.60985626</v>
+        <v>67.84394251000001</v>
       </c>
       <c r="D339" t="b">
         <v>1</v>
@@ -5187,13 +5187,13 @@
         <v>0</v>
       </c>
       <c r="B340" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C340" t="n">
-        <v>59.20328542</v>
+        <v>58.21765914</v>
       </c>
       <c r="D340" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="341">
@@ -5201,27 +5201,27 @@
         <v>0</v>
       </c>
       <c r="B341" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C341" t="n">
-        <v>14.85010267</v>
+        <v>49.70841889</v>
       </c>
       <c r="D341" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C342" t="n">
-        <v>12.12320329</v>
+        <v>8.410677617999999</v>
       </c>
       <c r="D342" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="343">
@@ -5232,10 +5232,10 @@
         <v>1</v>
       </c>
       <c r="C343" t="n">
-        <v>42.18480493</v>
+        <v>20.56673511</v>
       </c>
       <c r="D343" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="344">
@@ -5243,24 +5243,24 @@
         <v>0</v>
       </c>
       <c r="B344" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C344" t="n">
-        <v>9.691991786000001</v>
+        <v>24.3449692</v>
       </c>
       <c r="D344" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C345" t="n">
-        <v>164.5667351</v>
+        <v>21.15811088</v>
       </c>
       <c r="D345" t="b">
         <v>0</v>
@@ -5274,7 +5274,7 @@
         <v>1</v>
       </c>
       <c r="C346" t="n">
-        <v>5.125256674</v>
+        <v>23.45790554</v>
       </c>
       <c r="D346" t="b">
         <v>0</v>
@@ -5288,7 +5288,7 @@
         <v>1</v>
       </c>
       <c r="C347" t="n">
-        <v>52.10677618</v>
+        <v>35.84394251</v>
       </c>
       <c r="D347" t="b">
         <v>0</v>
@@ -5296,13 +5296,13 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C348" t="n">
-        <v>27.40041068</v>
+        <v>16.49281314</v>
       </c>
       <c r="D348" t="b">
         <v>0</v>
@@ -5316,10 +5316,10 @@
         <v>1</v>
       </c>
       <c r="C349" t="n">
-        <v>32.45995893</v>
+        <v>34.03696099</v>
       </c>
       <c r="D349" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="350">
@@ -5327,10 +5327,10 @@
         <v>0</v>
       </c>
       <c r="B350" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C350" t="n">
-        <v>59.99178645</v>
+        <v>34.49691992</v>
       </c>
       <c r="D350" t="b">
         <v>0</v>
@@ -5344,7 +5344,7 @@
         <v>0</v>
       </c>
       <c r="C351" t="n">
-        <v>90.51334702</v>
+        <v>22.73511294</v>
       </c>
       <c r="D351" t="b">
         <v>1</v>
@@ -5352,16 +5352,16 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B352" t="n">
         <v>0</v>
       </c>
       <c r="C352" t="n">
-        <v>9.790554415000001</v>
+        <v>81.64271047</v>
       </c>
       <c r="D352" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="353">
@@ -5372,10 +5372,10 @@
         <v>1</v>
       </c>
       <c r="C353" t="n">
-        <v>23.95071869</v>
+        <v>128.1314168</v>
       </c>
       <c r="D353" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354">
@@ -5386,10 +5386,10 @@
         <v>0</v>
       </c>
       <c r="C354" t="n">
-        <v>8.016427105</v>
+        <v>7.162217659</v>
       </c>
       <c r="D354" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="355">
@@ -5400,21 +5400,21 @@
         <v>1</v>
       </c>
       <c r="C355" t="n">
-        <v>12.8788501</v>
+        <v>115.5482546</v>
       </c>
       <c r="D355" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C356" t="n">
-        <v>14.71868583</v>
+        <v>17.60985626</v>
       </c>
       <c r="D356" t="b">
         <v>1</v>
@@ -5425,13 +5425,13 @@
         <v>0</v>
       </c>
       <c r="B357" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C357" t="n">
-        <v>23.2936345</v>
+        <v>6.800821355</v>
       </c>
       <c r="D357" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="358">
@@ -5442,10 +5442,10 @@
         <v>1</v>
       </c>
       <c r="C358" t="n">
-        <v>49.87268994</v>
+        <v>42.18480493</v>
       </c>
       <c r="D358" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359">
@@ -5456,7 +5456,7 @@
         <v>1</v>
       </c>
       <c r="C359" t="n">
-        <v>15.57289528</v>
+        <v>28.15605749</v>
       </c>
       <c r="D359" t="b">
         <v>1</v>
@@ -5464,16 +5464,16 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B360" t="n">
         <v>0</v>
       </c>
       <c r="C360" t="n">
-        <v>45.96303901</v>
+        <v>51.58110883</v>
       </c>
       <c r="D360" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="361">
@@ -5484,10 +5484,10 @@
         <v>0</v>
       </c>
       <c r="C361" t="n">
-        <v>56.77207392</v>
+        <v>3.811088296</v>
       </c>
       <c r="D361" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="362">
@@ -5498,7 +5498,7 @@
         <v>1</v>
       </c>
       <c r="C362" t="n">
-        <v>68.27104722999999</v>
+        <v>5.848049281</v>
       </c>
       <c r="D362" t="b">
         <v>1</v>
@@ -5506,16 +5506,16 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C363" t="n">
-        <v>13.10882957</v>
+        <v>15.60574949</v>
       </c>
       <c r="D363" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="364">
@@ -5523,13 +5523,13 @@
         <v>0</v>
       </c>
       <c r="B364" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C364" t="n">
-        <v>5.32238193</v>
+        <v>19.05544148</v>
       </c>
       <c r="D364" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="365">
@@ -5537,10 +5537,10 @@
         <v>0</v>
       </c>
       <c r="B365" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C365" t="n">
-        <v>16.78850103</v>
+        <v>73.13347023</v>
       </c>
       <c r="D365" t="b">
         <v>0</v>
@@ -5551,13 +5551,13 @@
         <v>0</v>
       </c>
       <c r="B366" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C366" t="n">
-        <v>13.9301848</v>
+        <v>89.00205339</v>
       </c>
       <c r="D366" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="367">
@@ -5565,10 +5565,10 @@
         <v>0</v>
       </c>
       <c r="B367" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C367" t="n">
-        <v>163.7782341</v>
+        <v>79.80287473999999</v>
       </c>
       <c r="D367" t="b">
         <v>0</v>
@@ -5582,7 +5582,7 @@
         <v>1</v>
       </c>
       <c r="C368" t="n">
-        <v>23.45790554</v>
+        <v>10.51334702</v>
       </c>
       <c r="D368" t="b">
         <v>0</v>
@@ -5590,13 +5590,13 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B369" t="n">
         <v>0</v>
       </c>
       <c r="C369" t="n">
-        <v>5.158110883</v>
+        <v>9.034907598</v>
       </c>
       <c r="D369" t="b">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>1</v>
       </c>
       <c r="C370" t="n">
-        <v>7.819301848</v>
+        <v>63.54004107</v>
       </c>
       <c r="D370" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="371">
@@ -5624,7 +5624,7 @@
         <v>1</v>
       </c>
       <c r="C371" t="n">
-        <v>21.35523614</v>
+        <v>10.84188912</v>
       </c>
       <c r="D371" t="b">
         <v>1</v>
@@ -5632,27 +5632,27 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B372" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C372" t="n">
-        <v>42.48049281</v>
+        <v>27.4661191</v>
       </c>
       <c r="D372" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C373" t="n">
-        <v>18.16837782</v>
+        <v>8.87063655</v>
       </c>
       <c r="D373" t="b">
         <v>1</v>
@@ -5660,13 +5660,13 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C374" t="n">
-        <v>15.01437372</v>
+        <v>128.0657084</v>
       </c>
       <c r="D374" t="b">
         <v>0</v>
@@ -5677,27 +5677,27 @@
         <v>0</v>
       </c>
       <c r="B375" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C375" t="n">
-        <v>28.58316222</v>
+        <v>32.88706366</v>
       </c>
       <c r="D375" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B376" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C376" t="n">
-        <v>63.14579055</v>
+        <v>15.93429158</v>
       </c>
       <c r="D376" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="377">
@@ -5708,35 +5708,35 @@
         <v>1</v>
       </c>
       <c r="C377" t="n">
-        <v>44.78028747</v>
+        <v>60.78028747</v>
       </c>
       <c r="D377" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B378" t="n">
         <v>0</v>
       </c>
       <c r="C378" t="n">
-        <v>85.48665298</v>
+        <v>5.650924025</v>
       </c>
       <c r="D378" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B379" t="n">
         <v>0</v>
       </c>
       <c r="C379" t="n">
-        <v>3.58110883</v>
+        <v>9.790554415000001</v>
       </c>
       <c r="D379" t="b">
         <v>1</v>
@@ -5744,13 +5744,13 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B380" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C380" t="n">
-        <v>21.88090349</v>
+        <v>18.7926078</v>
       </c>
       <c r="D380" t="b">
         <v>0</v>
@@ -5764,24 +5764,24 @@
         <v>1</v>
       </c>
       <c r="C381" t="n">
-        <v>12.09034908</v>
+        <v>36.73100616</v>
       </c>
       <c r="D381" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C382" t="n">
-        <v>11.76180698</v>
+        <v>13.17453799</v>
       </c>
       <c r="D382" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="383">
@@ -5789,10 +5789,10 @@
         <v>0</v>
       </c>
       <c r="B383" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C383" t="n">
-        <v>10.38193018</v>
+        <v>94.12731006</v>
       </c>
       <c r="D383" t="b">
         <v>0</v>
@@ -5800,13 +5800,13 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B384" t="n">
         <v>0</v>
       </c>
       <c r="C384" t="n">
-        <v>8.213552361</v>
+        <v>27.56468172</v>
       </c>
       <c r="D384" t="b">
         <v>0</v>
@@ -5814,13 +5814,13 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B385" t="n">
         <v>1</v>
       </c>
       <c r="C385" t="n">
-        <v>17.57700205</v>
+        <v>53.19096509</v>
       </c>
       <c r="D385" t="b">
         <v>1</v>
@@ -5834,7 +5834,7 @@
         <v>1</v>
       </c>
       <c r="C386" t="n">
-        <v>23.45790554</v>
+        <v>1.80698152</v>
       </c>
       <c r="D386" t="b">
         <v>0</v>
@@ -5842,16 +5842,16 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B387" t="n">
         <v>0</v>
       </c>
       <c r="C387" t="n">
-        <v>4.435318275</v>
+        <v>18.56262834</v>
       </c>
       <c r="D387" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="388">
@@ -5859,24 +5859,24 @@
         <v>1</v>
       </c>
       <c r="B388" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C388" t="n">
-        <v>38.53798768</v>
+        <v>3.416837782</v>
       </c>
       <c r="D388" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B389" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C389" t="n">
-        <v>40.87063655</v>
+        <v>26.94045175</v>
       </c>
       <c r="D389" t="b">
         <v>1</v>
@@ -5890,7 +5890,7 @@
         <v>1</v>
       </c>
       <c r="C390" t="n">
-        <v>4.928131417</v>
+        <v>45.07597536</v>
       </c>
       <c r="D390" t="b">
         <v>0</v>
@@ -5898,16 +5898,16 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B391" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C391" t="n">
-        <v>20.92813142</v>
+        <v>49.7412731</v>
       </c>
       <c r="D391" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392">
@@ -5918,7 +5918,7 @@
         <v>1</v>
       </c>
       <c r="C392" t="n">
-        <v>9.100616016</v>
+        <v>4.960985626</v>
       </c>
       <c r="D392" t="b">
         <v>1</v>
@@ -5926,13 +5926,13 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B393" t="n">
         <v>1</v>
       </c>
       <c r="C393" t="n">
-        <v>39.22792608</v>
+        <v>41.69199179</v>
       </c>
       <c r="D393" t="b">
         <v>1</v>
@@ -5946,10 +5946,10 @@
         <v>0</v>
       </c>
       <c r="C394" t="n">
-        <v>4.1724846</v>
+        <v>54.07802875</v>
       </c>
       <c r="D394" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="395">
@@ -5957,13 +5957,13 @@
         <v>0</v>
       </c>
       <c r="B395" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C395" t="n">
-        <v>36.23819302</v>
+        <v>0.492813142</v>
       </c>
       <c r="D395" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="396">
@@ -5971,27 +5971,27 @@
         <v>0</v>
       </c>
       <c r="B396" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C396" t="n">
-        <v>16.22997947</v>
+        <v>26.67761807</v>
       </c>
       <c r="D396" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B397" t="n">
         <v>0</v>
       </c>
       <c r="C397" t="n">
-        <v>11.76180698</v>
+        <v>25.98767967</v>
       </c>
       <c r="D397" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="398">
@@ -6002,7 +6002,7 @@
         <v>1</v>
       </c>
       <c r="C398" t="n">
-        <v>8.739219713000001</v>
+        <v>3.121149897</v>
       </c>
       <c r="D398" t="b">
         <v>0</v>
@@ -6016,7 +6016,7 @@
         <v>0</v>
       </c>
       <c r="C399" t="n">
-        <v>72.57494867</v>
+        <v>6.078028747</v>
       </c>
       <c r="D399" t="b">
         <v>0</v>
@@ -6027,10 +6027,10 @@
         <v>0</v>
       </c>
       <c r="B400" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C400" t="n">
-        <v>67.4825462</v>
+        <v>11.79466119</v>
       </c>
       <c r="D400" t="b">
         <v>0</v>
@@ -6038,13 +6038,13 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B401" t="n">
         <v>0</v>
       </c>
       <c r="C401" t="n">
-        <v>41.65913758</v>
+        <v>7.852156057</v>
       </c>
       <c r="D401" t="b">
         <v>0</v>
@@ -6058,10 +6058,10 @@
         <v>1</v>
       </c>
       <c r="C402" t="n">
-        <v>1.971252567</v>
+        <v>8.607802875000001</v>
       </c>
       <c r="D402" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="403">
@@ -6072,7 +6072,7 @@
         <v>1</v>
       </c>
       <c r="C403" t="n">
-        <v>118.899384</v>
+        <v>12.78028747</v>
       </c>
       <c r="D403" t="b">
         <v>1</v>
@@ -6086,7 +6086,7 @@
         <v>0</v>
       </c>
       <c r="C404" t="n">
-        <v>59.00616016</v>
+        <v>22.73511294</v>
       </c>
       <c r="D404" t="b">
         <v>1</v>
@@ -6094,13 +6094,13 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B405" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C405" t="n">
-        <v>11.26899384</v>
+        <v>1.347022587</v>
       </c>
       <c r="D405" t="b">
         <v>0</v>
@@ -6114,7 +6114,7 @@
         <v>1</v>
       </c>
       <c r="C406" t="n">
-        <v>36.59958932</v>
+        <v>2.39835729</v>
       </c>
       <c r="D406" t="b">
         <v>0</v>
@@ -6122,16 +6122,16 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C407" t="n">
-        <v>15.86858316</v>
+        <v>15.14579055</v>
       </c>
       <c r="D407" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="408">
@@ -6139,13 +6139,13 @@
         <v>0</v>
       </c>
       <c r="B408" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C408" t="n">
-        <v>45.73305955</v>
+        <v>23.9835729</v>
       </c>
       <c r="D408" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="409">
@@ -6156,7 +6156,7 @@
         <v>1</v>
       </c>
       <c r="C409" t="n">
-        <v>16.39425051</v>
+        <v>23.95071869</v>
       </c>
       <c r="D409" t="b">
         <v>1</v>
@@ -6170,7 +6170,7 @@
         <v>1</v>
       </c>
       <c r="C410" t="n">
-        <v>155.3675565</v>
+        <v>13.73305955</v>
       </c>
       <c r="D410" t="b">
         <v>0</v>
@@ -6178,13 +6178,13 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B411" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C411" t="n">
-        <v>58.94045175</v>
+        <v>33.57700205</v>
       </c>
       <c r="D411" t="b">
         <v>0</v>
@@ -6198,10 +6198,10 @@
         <v>1</v>
       </c>
       <c r="C412" t="n">
-        <v>1.445585216</v>
+        <v>34.56262834</v>
       </c>
       <c r="D412" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="413">
@@ -6212,10 +6212,10 @@
         <v>1</v>
       </c>
       <c r="C413" t="n">
-        <v>13.5687885</v>
+        <v>7.12936345</v>
       </c>
       <c r="D413" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="414">
@@ -6226,21 +6226,21 @@
         <v>1</v>
       </c>
       <c r="C414" t="n">
-        <v>39.06365503</v>
+        <v>70.93223819000001</v>
       </c>
       <c r="D414" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B415" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C415" t="n">
-        <v>17.93839836</v>
+        <v>123.0718686</v>
       </c>
       <c r="D415" t="b">
         <v>1</v>
@@ -6254,7 +6254,7 @@
         <v>1</v>
       </c>
       <c r="C416" t="n">
-        <v>16.78850103</v>
+        <v>48.09856263</v>
       </c>
       <c r="D416" t="b">
         <v>1</v>
@@ -6262,13 +6262,13 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B417" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C417" t="n">
-        <v>15.11293634</v>
+        <v>44.48459959</v>
       </c>
       <c r="D417" t="b">
         <v>0</v>
@@ -6279,13 +6279,13 @@
         <v>0</v>
       </c>
       <c r="B418" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C418" t="n">
-        <v>22.47227926</v>
+        <v>36.59958932</v>
       </c>
       <c r="D418" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="419">
@@ -6296,7 +6296,7 @@
         <v>0</v>
       </c>
       <c r="C419" t="n">
-        <v>155.1704312</v>
+        <v>12.05749487</v>
       </c>
       <c r="D419" t="b">
         <v>1</v>
@@ -6304,16 +6304,16 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B420" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C420" t="n">
-        <v>24.08213552</v>
+        <v>103.5893224</v>
       </c>
       <c r="D420" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="421">
@@ -6321,10 +6321,10 @@
         <v>0</v>
       </c>
       <c r="B421" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C421" t="n">
-        <v>17.24845996</v>
+        <v>82.7926078</v>
       </c>
       <c r="D421" t="b">
         <v>0</v>
@@ -6338,21 +6338,21 @@
         <v>1</v>
       </c>
       <c r="C422" t="n">
-        <v>8.640657084000001</v>
+        <v>101.5195072</v>
       </c>
       <c r="D422" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B423" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C423" t="n">
-        <v>60.78028747</v>
+        <v>11.56468172</v>
       </c>
       <c r="D423" t="b">
         <v>0</v>
@@ -6360,13 +6360,13 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B424" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C424" t="n">
-        <v>105.9219713</v>
+        <v>7.950718686</v>
       </c>
       <c r="D424" t="b">
         <v>0</v>
@@ -6380,7 +6380,7 @@
         <v>1</v>
       </c>
       <c r="C425" t="n">
-        <v>2.168377823</v>
+        <v>46.9486653</v>
       </c>
       <c r="D425" t="b">
         <v>0</v>
@@ -6391,10 +6391,10 @@
         <v>0</v>
       </c>
       <c r="B426" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C426" t="n">
-        <v>52.00821355</v>
+        <v>65.37987680000001</v>
       </c>
       <c r="D426" t="b">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>1</v>
       </c>
       <c r="C427" t="n">
-        <v>11.69609856</v>
+        <v>44.02464066</v>
       </c>
       <c r="D427" t="b">
         <v>1</v>
@@ -6416,16 +6416,16 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B428" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C428" t="n">
-        <v>23.19507187</v>
+        <v>12.25462012</v>
       </c>
       <c r="D428" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="429">
@@ -6436,7 +6436,7 @@
         <v>1</v>
       </c>
       <c r="C429" t="n">
-        <v>19.31827515</v>
+        <v>39.68788501</v>
       </c>
       <c r="D429" t="b">
         <v>0</v>
@@ -6444,16 +6444,16 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B430" t="n">
         <v>1</v>
       </c>
       <c r="C430" t="n">
-        <v>26.18480493</v>
+        <v>50.23408624</v>
       </c>
       <c r="D430" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="431">
@@ -6461,13 +6461,13 @@
         <v>0</v>
       </c>
       <c r="B431" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C431" t="n">
-        <v>70.34086241999999</v>
+        <v>13.40451745</v>
       </c>
       <c r="D431" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="432">
@@ -6478,7 +6478,7 @@
         <v>0</v>
       </c>
       <c r="C432" t="n">
-        <v>18.95687885</v>
+        <v>13.40451745</v>
       </c>
       <c r="D432" t="b">
         <v>1</v>
@@ -6486,44 +6486,44 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B433" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C433" t="n">
-        <v>23.95071869</v>
+        <v>9.067761807</v>
       </c>
       <c r="D433" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B434" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C434" t="n">
-        <v>32.49281314</v>
+        <v>40.31211499</v>
       </c>
       <c r="D434" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B435" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C435" t="n">
-        <v>5.815195072</v>
+        <v>16.06570842</v>
       </c>
       <c r="D435" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="436">
@@ -6534,10 +6534,10 @@
         <v>1</v>
       </c>
       <c r="C436" t="n">
-        <v>2.431211499</v>
+        <v>38.86652977</v>
       </c>
       <c r="D436" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="437">
@@ -6548,21 +6548,21 @@
         <v>1</v>
       </c>
       <c r="C437" t="n">
-        <v>33.90554415</v>
+        <v>22.63655031</v>
       </c>
       <c r="D437" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B438" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C438" t="n">
-        <v>19.84394251</v>
+        <v>9.199178645</v>
       </c>
       <c r="D438" t="b">
         <v>1</v>
@@ -6576,35 +6576,35 @@
         <v>1</v>
       </c>
       <c r="C439" t="n">
-        <v>6.669404517</v>
+        <v>40.37782341</v>
       </c>
       <c r="D439" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B440" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C440" t="n">
-        <v>22.24229979</v>
+        <v>42.38193018</v>
       </c>
       <c r="D440" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B441" t="n">
         <v>0</v>
       </c>
       <c r="C441" t="n">
-        <v>49.31416838</v>
+        <v>61.73305955</v>
       </c>
       <c r="D441" t="b">
         <v>1</v>
@@ -6612,16 +6612,16 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B442" t="n">
         <v>0</v>
       </c>
       <c r="C442" t="n">
-        <v>5.848049281</v>
+        <v>46.35728953</v>
       </c>
       <c r="D442" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="443">
@@ -6629,10 +6629,10 @@
         <v>0</v>
       </c>
       <c r="B443" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C443" t="n">
-        <v>14.98151951</v>
+        <v>3.975359343</v>
       </c>
       <c r="D443" t="b">
         <v>1</v>
@@ -6640,27 +6640,27 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B444" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C444" t="n">
-        <v>16.42710472</v>
+        <v>51.31827515</v>
       </c>
       <c r="D444" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C445" t="n">
-        <v>6.045174538</v>
+        <v>27.92607803</v>
       </c>
       <c r="D445" t="b">
         <v>0</v>
@@ -6671,27 +6671,27 @@
         <v>0</v>
       </c>
       <c r="B446" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C446" t="n">
-        <v>37.38809035</v>
+        <v>78.68583162</v>
       </c>
       <c r="D446" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B447" t="n">
         <v>0</v>
       </c>
       <c r="C447" t="n">
-        <v>52.73100616</v>
+        <v>61.07597536</v>
       </c>
       <c r="D447" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="448">
@@ -6699,10 +6699,10 @@
         <v>0</v>
       </c>
       <c r="B448" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C448" t="n">
-        <v>86.66940452</v>
+        <v>79.54004107</v>
       </c>
       <c r="D448" t="b">
         <v>0</v>
@@ -6716,7 +6716,7 @@
         <v>1</v>
       </c>
       <c r="C449" t="n">
-        <v>27.36755647</v>
+        <v>166.275154</v>
       </c>
       <c r="D449" t="b">
         <v>1</v>
@@ -6724,16 +6724,16 @@
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B450" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C450" t="n">
-        <v>7.523613963</v>
+        <v>3.811088296</v>
       </c>
       <c r="D450" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="451">
@@ -6744,10 +6744,10 @@
         <v>1</v>
       </c>
       <c r="C451" t="n">
-        <v>54.9650924</v>
+        <v>34.56262834</v>
       </c>
       <c r="D451" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="452">
@@ -6755,13 +6755,13 @@
         <v>0</v>
       </c>
       <c r="B452" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C452" t="n">
-        <v>50.98973306</v>
+        <v>9.429158111</v>
       </c>
       <c r="D452" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="453">
@@ -6772,10 +6772,10 @@
         <v>1</v>
       </c>
       <c r="C453" t="n">
-        <v>33.41273101</v>
+        <v>68.27104722999999</v>
       </c>
       <c r="D453" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="454">
@@ -6783,10 +6783,10 @@
         <v>0</v>
       </c>
       <c r="B454" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C454" t="n">
-        <v>5.585215606</v>
+        <v>5.9137577</v>
       </c>
       <c r="D454" t="b">
         <v>0</v>
@@ -6794,27 +6794,27 @@
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B455" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C455" t="n">
-        <v>99.77823409</v>
+        <v>5.420944559</v>
       </c>
       <c r="D455" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B456" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C456" t="n">
-        <v>32.85420945</v>
+        <v>6.53798768</v>
       </c>
       <c r="D456" t="b">
         <v>1</v>
@@ -6825,10 +6825,10 @@
         <v>0</v>
       </c>
       <c r="B457" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C457" t="n">
-        <v>70.93223819000001</v>
+        <v>3.975359343</v>
       </c>
       <c r="D457" t="b">
         <v>1</v>
@@ -6839,10 +6839,10 @@
         <v>0</v>
       </c>
       <c r="B458" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C458" t="n">
-        <v>11.49897331</v>
+        <v>73.49486653</v>
       </c>
       <c r="D458" t="b">
         <v>1</v>
@@ -6856,7 +6856,7 @@
         <v>1</v>
       </c>
       <c r="C459" t="n">
-        <v>70.83367556</v>
+        <v>6.275154004</v>
       </c>
       <c r="D459" t="b">
         <v>1</v>
@@ -6867,10 +6867,10 @@
         <v>0</v>
       </c>
       <c r="B460" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C460" t="n">
-        <v>86.04517454</v>
+        <v>35.84394251</v>
       </c>
       <c r="D460" t="b">
         <v>0</v>
@@ -6881,13 +6881,13 @@
         <v>0</v>
       </c>
       <c r="B461" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C461" t="n">
-        <v>35.28542094</v>
+        <v>0.689938398</v>
       </c>
       <c r="D461" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="462">
@@ -6895,13 +6895,13 @@
         <v>0</v>
       </c>
       <c r="B462" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C462" t="n">
-        <v>84.04106776</v>
+        <v>49.14989733</v>
       </c>
       <c r="D462" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="463">
@@ -6912,7 +6912,7 @@
         <v>1</v>
       </c>
       <c r="C463" t="n">
-        <v>20.89527721</v>
+        <v>36.59958932</v>
       </c>
       <c r="D463" t="b">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="C464" t="n">
-        <v>45.30595483</v>
+        <v>30.12731006</v>
       </c>
       <c r="D464" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="465">
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="C465" t="n">
-        <v>15.70431211</v>
+        <v>72.67351128999999</v>
       </c>
       <c r="D465" t="b">
         <v>0</v>
@@ -6954,7 +6954,7 @@
         <v>1</v>
       </c>
       <c r="C466" t="n">
-        <v>5.519507187</v>
+        <v>8.180698152</v>
       </c>
       <c r="D466" t="b">
         <v>0</v>
@@ -6962,13 +6962,13 @@
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B467" t="n">
         <v>1</v>
       </c>
       <c r="C467" t="n">
-        <v>23.6550308</v>
+        <v>6.439425051</v>
       </c>
       <c r="D467" t="b">
         <v>1</v>
@@ -6979,10 +6979,10 @@
         <v>0</v>
       </c>
       <c r="B468" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C468" t="n">
-        <v>3.482546201</v>
+        <v>95.21149896999999</v>
       </c>
       <c r="D468" t="b">
         <v>1</v>
@@ -6996,7 +6996,7 @@
         <v>1</v>
       </c>
       <c r="C469" t="n">
-        <v>40.3449692</v>
+        <v>38.76796715</v>
       </c>
       <c r="D469" t="b">
         <v>1</v>
@@ -7004,16 +7004,16 @@
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B470" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C470" t="n">
-        <v>2.759753593</v>
+        <v>110.4887064</v>
       </c>
       <c r="D470" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="471">
@@ -7024,21 +7024,21 @@
         <v>0</v>
       </c>
       <c r="C471" t="n">
-        <v>45.30595483</v>
+        <v>0.492813142</v>
       </c>
       <c r="D471" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B472" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C472" t="n">
-        <v>9.100616016</v>
+        <v>29.24024641</v>
       </c>
       <c r="D472" t="b">
         <v>1</v>
@@ -7052,7 +7052,7 @@
         <v>1</v>
       </c>
       <c r="C473" t="n">
-        <v>11.23613963</v>
+        <v>20.96098563</v>
       </c>
       <c r="D473" t="b">
         <v>1</v>
@@ -7063,13 +7063,13 @@
         <v>0</v>
       </c>
       <c r="B474" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C474" t="n">
-        <v>5.848049281</v>
+        <v>1.708418891</v>
       </c>
       <c r="D474" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="475">
@@ -7077,10 +7077,10 @@
         <v>0</v>
       </c>
       <c r="B475" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C475" t="n">
-        <v>18.49691992</v>
+        <v>58.80903491</v>
       </c>
       <c r="D475" t="b">
         <v>1</v>
@@ -7091,13 +7091,13 @@
         <v>0</v>
       </c>
       <c r="B476" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C476" t="n">
-        <v>8.410677617999999</v>
+        <v>11.72895277</v>
       </c>
       <c r="D476" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="477">
@@ -7108,7 +7108,7 @@
         <v>1</v>
       </c>
       <c r="C477" t="n">
-        <v>49.47843943</v>
+        <v>30.22587269</v>
       </c>
       <c r="D477" t="b">
         <v>0</v>
@@ -7116,13 +7116,13 @@
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B478" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C478" t="n">
-        <v>49.41273101</v>
+        <v>179.449692</v>
       </c>
       <c r="D478" t="b">
         <v>0</v>
@@ -7136,10 +7136,10 @@
         <v>1</v>
       </c>
       <c r="C479" t="n">
-        <v>105.8234086</v>
+        <v>22.9650924</v>
       </c>
       <c r="D479" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480">
@@ -7147,10 +7147,10 @@
         <v>0</v>
       </c>
       <c r="B480" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C480" t="n">
-        <v>59.99178645</v>
+        <v>23.55646817</v>
       </c>
       <c r="D480" t="b">
         <v>0</v>
@@ -7164,7 +7164,7 @@
         <v>1</v>
       </c>
       <c r="C481" t="n">
-        <v>58.94045175</v>
+        <v>14.55441478</v>
       </c>
       <c r="D481" t="b">
         <v>0</v>
@@ -7178,21 +7178,21 @@
         <v>0</v>
       </c>
       <c r="C482" t="n">
-        <v>17.11704312</v>
+        <v>59.20328542</v>
       </c>
       <c r="D482" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B483" t="n">
         <v>1</v>
       </c>
       <c r="C483" t="n">
-        <v>81.24845996000001</v>
+        <v>5.94661191</v>
       </c>
       <c r="D483" t="b">
         <v>0</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="B484" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C484" t="n">
-        <v>50.29979466</v>
+        <v>15.34291581</v>
       </c>
       <c r="D484" t="b">
         <v>0</v>
@@ -7214,13 +7214,13 @@
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B485" t="n">
         <v>0</v>
       </c>
       <c r="C485" t="n">
-        <v>7.852156057</v>
+        <v>3.482546201</v>
       </c>
       <c r="D485" t="b">
         <v>0</v>
@@ -7231,38 +7231,38 @@
         <v>0</v>
       </c>
       <c r="B486" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C486" t="n">
-        <v>23.9835729</v>
+        <v>23.2936345</v>
       </c>
       <c r="D486" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C487" t="n">
-        <v>3.449691992</v>
+        <v>94.78439425000001</v>
       </c>
       <c r="D487" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B488" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C488" t="n">
-        <v>110.0287474</v>
+        <v>30.78439425</v>
       </c>
       <c r="D488" t="b">
         <v>0</v>
@@ -7273,10 +7273,10 @@
         <v>0</v>
       </c>
       <c r="B489" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C489" t="n">
-        <v>11.53182752</v>
+        <v>149.6180698</v>
       </c>
       <c r="D489" t="b">
         <v>0</v>
@@ -7290,7 +7290,7 @@
         <v>1</v>
       </c>
       <c r="C490" t="n">
-        <v>10.94045175</v>
+        <v>16.59137577</v>
       </c>
       <c r="D490" t="b">
         <v>1</v>
@@ -7301,10 +7301,10 @@
         <v>0</v>
       </c>
       <c r="B491" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C491" t="n">
-        <v>3.975359343</v>
+        <v>74.74332649</v>
       </c>
       <c r="D491" t="b">
         <v>1</v>
@@ -7318,7 +7318,7 @@
         <v>1</v>
       </c>
       <c r="C492" t="n">
-        <v>112.788501</v>
+        <v>2.234086242</v>
       </c>
       <c r="D492" t="b">
         <v>0</v>
@@ -7332,10 +7332,10 @@
         <v>1</v>
       </c>
       <c r="C493" t="n">
-        <v>8.772073922000001</v>
+        <v>20.04106776</v>
       </c>
       <c r="D493" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="494">
@@ -7343,10 +7343,10 @@
         <v>0</v>
       </c>
       <c r="B494" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C494" t="n">
-        <v>39.88501027</v>
+        <v>49.80698152</v>
       </c>
       <c r="D494" t="b">
         <v>0</v>
@@ -7357,24 +7357,24 @@
         <v>0</v>
       </c>
       <c r="B495" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C495" t="n">
-        <v>16.95277207</v>
+        <v>14.85010267</v>
       </c>
       <c r="D495" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B496" t="n">
         <v>1</v>
       </c>
       <c r="C496" t="n">
-        <v>3.975359343</v>
+        <v>39.22792608</v>
       </c>
       <c r="D496" t="b">
         <v>1</v>
@@ -7385,13 +7385,13 @@
         <v>0</v>
       </c>
       <c r="B497" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C497" t="n">
-        <v>14.45585216</v>
+        <v>11.89322382</v>
       </c>
       <c r="D497" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="498">
@@ -7402,10 +7402,10 @@
         <v>1</v>
       </c>
       <c r="C498" t="n">
-        <v>32.45995893</v>
+        <v>16.65708419</v>
       </c>
       <c r="D498" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="499">
@@ -7416,24 +7416,24 @@
         <v>1</v>
       </c>
       <c r="C499" t="n">
-        <v>10.7761807</v>
+        <v>82.75975359</v>
       </c>
       <c r="D499" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B500" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C500" t="n">
-        <v>26.0862423</v>
+        <v>55.95071869</v>
       </c>
       <c r="D500" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="501">
@@ -7441,24 +7441,24 @@
         <v>0</v>
       </c>
       <c r="B501" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C501" t="n">
-        <v>144.7556468</v>
+        <v>26.94045175</v>
       </c>
       <c r="D501" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B502" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C502" t="n">
-        <v>10.02053388</v>
+        <v>12.32032854</v>
       </c>
       <c r="D502" t="b">
         <v>0</v>
@@ -7466,13 +7466,13 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B503" t="n">
         <v>0</v>
       </c>
       <c r="C503" t="n">
-        <v>123.6960986</v>
+        <v>16.95277207</v>
       </c>
       <c r="D503" t="b">
         <v>0</v>
@@ -7480,13 +7480,13 @@
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B504" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C504" t="n">
-        <v>20.92813142</v>
+        <v>3.252566735</v>
       </c>
       <c r="D504" t="b">
         <v>1</v>
@@ -7500,7 +7500,7 @@
         <v>1</v>
       </c>
       <c r="C505" t="n">
-        <v>45.37166324</v>
+        <v>79.86858316</v>
       </c>
       <c r="D505" t="b">
         <v>1</v>
@@ -7514,7 +7514,7 @@
         <v>1</v>
       </c>
       <c r="C506" t="n">
-        <v>8.344969198999999</v>
+        <v>3.876796715</v>
       </c>
       <c r="D506" t="b">
         <v>0</v>
@@ -7522,13 +7522,13 @@
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B507" t="n">
         <v>0</v>
       </c>
       <c r="C507" t="n">
-        <v>14.48870637</v>
+        <v>19.35112936</v>
       </c>
       <c r="D507" t="b">
         <v>0</v>
@@ -7536,16 +7536,16 @@
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B508" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C508" t="n">
-        <v>33.67556468</v>
+        <v>54.01232033</v>
       </c>
       <c r="D508" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="509">
@@ -7553,10 +7553,10 @@
         <v>0</v>
       </c>
       <c r="B509" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C509" t="n">
-        <v>14.48870637</v>
+        <v>40.04928131</v>
       </c>
       <c r="D509" t="b">
         <v>0</v>
@@ -7564,13 +7564,13 @@
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B510" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C510" t="n">
-        <v>15.14579055</v>
+        <v>64.75564682</v>
       </c>
       <c r="D510" t="b">
         <v>0</v>
@@ -7581,24 +7581,24 @@
         <v>0</v>
       </c>
       <c r="B511" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C511" t="n">
-        <v>33.93839836</v>
+        <v>32.88706366</v>
       </c>
       <c r="D511" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B512" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C512" t="n">
-        <v>33.28131417</v>
+        <v>3.121149897</v>
       </c>
       <c r="D512" t="b">
         <v>0</v>
@@ -7606,16 +7606,16 @@
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B513" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C513" t="n">
-        <v>16.65708419</v>
+        <v>116.7310062</v>
       </c>
       <c r="D513" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="514">
@@ -7623,10 +7623,10 @@
         <v>0</v>
       </c>
       <c r="B514" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C514" t="n">
-        <v>22.73511294</v>
+        <v>13.01026694</v>
       </c>
       <c r="D514" t="b">
         <v>1</v>
@@ -7637,10 +7637,10 @@
         <v>0</v>
       </c>
       <c r="B515" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C515" t="n">
-        <v>12.8788501</v>
+        <v>70.30800821</v>
       </c>
       <c r="D515" t="b">
         <v>1</v>
@@ -7654,7 +7654,7 @@
         <v>0</v>
       </c>
       <c r="C516" t="n">
-        <v>27.56468172</v>
+        <v>12.64887064</v>
       </c>
       <c r="D516" t="b">
         <v>0</v>
@@ -7668,7 +7668,7 @@
         <v>1</v>
       </c>
       <c r="C517" t="n">
-        <v>42.57905544</v>
+        <v>25.36344969</v>
       </c>
       <c r="D517" t="b">
         <v>0</v>
@@ -7676,16 +7676,16 @@
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B518" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C518" t="n">
-        <v>22.24229979</v>
+        <v>42.38193018</v>
       </c>
       <c r="D518" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="519">
@@ -7693,10 +7693,10 @@
         <v>0</v>
       </c>
       <c r="B519" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C519" t="n">
-        <v>4.501026694</v>
+        <v>31.34291581</v>
       </c>
       <c r="D519" t="b">
         <v>0</v>
@@ -7704,13 +7704,13 @@
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B520" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C520" t="n">
-        <v>12.78028747</v>
+        <v>12.35318275</v>
       </c>
       <c r="D520" t="b">
         <v>1</v>
@@ -7724,7 +7724,7 @@
         <v>1</v>
       </c>
       <c r="C521" t="n">
-        <v>79.86858316</v>
+        <v>26.31622177</v>
       </c>
       <c r="D521" t="b">
         <v>1</v>
@@ -7732,41 +7732,41 @@
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B522" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C522" t="n">
-        <v>14.06160164</v>
+        <v>25.42915811</v>
       </c>
       <c r="D522" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B523" t="n">
         <v>0</v>
       </c>
       <c r="C523" t="n">
-        <v>16.95277207</v>
+        <v>23.6550308</v>
       </c>
       <c r="D523" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B524" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C524" t="n">
-        <v>5.026694045</v>
+        <v>0.755646817</v>
       </c>
       <c r="D524" t="b">
         <v>1</v>
@@ -7777,10 +7777,10 @@
         <v>0</v>
       </c>
       <c r="B525" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C525" t="n">
-        <v>19.74537988</v>
+        <v>48.6899384</v>
       </c>
       <c r="D525" t="b">
         <v>0</v>
@@ -7788,27 +7788,27 @@
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B526" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C526" t="n">
-        <v>48.19712526</v>
+        <v>70.83367556</v>
       </c>
       <c r="D526" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B527" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C527" t="n">
-        <v>10.61190965</v>
+        <v>40.3449692</v>
       </c>
       <c r="D527" t="b">
         <v>0</v>
@@ -7819,10 +7819,10 @@
         <v>0</v>
       </c>
       <c r="B528" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C528" t="n">
-        <v>31.96714579</v>
+        <v>82.82546201</v>
       </c>
       <c r="D528" t="b">
         <v>1</v>
@@ -7833,13 +7833,13 @@
         <v>0</v>
       </c>
       <c r="B529" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C529" t="n">
-        <v>132.8952772</v>
+        <v>11.99178645</v>
       </c>
       <c r="D529" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="530">
@@ -7850,7 +7850,7 @@
         <v>0</v>
       </c>
       <c r="C530" t="n">
-        <v>32.32854209</v>
+        <v>12.5174538</v>
       </c>
       <c r="D530" t="b">
         <v>0</v>
@@ -7864,7 +7864,7 @@
         <v>1</v>
       </c>
       <c r="C531" t="n">
-        <v>26.4476386</v>
+        <v>51.87679671</v>
       </c>
       <c r="D531" t="b">
         <v>1</v>
@@ -7872,16 +7872,16 @@
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B532" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C532" t="n">
-        <v>51.94250513</v>
+        <v>3.449691992</v>
       </c>
       <c r="D532" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="533">
@@ -7892,10 +7892,10 @@
         <v>1</v>
       </c>
       <c r="C533" t="n">
-        <v>44.97741273</v>
+        <v>27.36755647</v>
       </c>
       <c r="D533" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="534">
@@ -7906,10 +7906,10 @@
         <v>1</v>
       </c>
       <c r="C534" t="n">
-        <v>19.71252567</v>
+        <v>66.7926078</v>
       </c>
       <c r="D534" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="535">
@@ -7920,7 +7920,7 @@
         <v>1</v>
       </c>
       <c r="C535" t="n">
-        <v>4.073921971</v>
+        <v>19.18685832</v>
       </c>
       <c r="D535" t="b">
         <v>1</v>
@@ -7928,16 +7928,16 @@
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B536" t="n">
         <v>0</v>
       </c>
       <c r="C536" t="n">
-        <v>7.162217659</v>
+        <v>11.95893224</v>
       </c>
       <c r="D536" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="537">
@@ -7948,10 +7948,10 @@
         <v>0</v>
       </c>
       <c r="C537" t="n">
-        <v>26.21765914</v>
+        <v>53.42094456</v>
       </c>
       <c r="D537" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="538">
@@ -7962,10 +7962,10 @@
         <v>1</v>
       </c>
       <c r="C538" t="n">
-        <v>11.49897331</v>
+        <v>24.47638604</v>
       </c>
       <c r="D538" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="539">
@@ -7973,13 +7973,13 @@
         <v>0</v>
       </c>
       <c r="B539" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C539" t="n">
-        <v>17.41273101</v>
+        <v>44.94455852</v>
       </c>
       <c r="D539" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="540">
@@ -7987,13 +7987,13 @@
         <v>0</v>
       </c>
       <c r="B540" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C540" t="n">
-        <v>16.85420945</v>
+        <v>22.57084189</v>
       </c>
       <c r="D540" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="541">
@@ -8001,10 +8001,10 @@
         <v>0</v>
       </c>
       <c r="B541" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C541" t="n">
-        <v>43.92607803</v>
+        <v>13.8973306</v>
       </c>
       <c r="D541" t="b">
         <v>1</v>
@@ -8012,13 +8012,13 @@
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B542" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C542" t="n">
-        <v>14.6201232</v>
+        <v>89.19917864</v>
       </c>
       <c r="D542" t="b">
         <v>1</v>
@@ -8029,13 +8029,13 @@
         <v>0</v>
       </c>
       <c r="B543" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C543" t="n">
-        <v>27.23613963</v>
+        <v>48.45995893</v>
       </c>
       <c r="D543" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="544">
@@ -8043,13 +8043,13 @@
         <v>0</v>
       </c>
       <c r="B544" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C544" t="n">
-        <v>6.176591376</v>
+        <v>22.70225873</v>
       </c>
       <c r="D544" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="545">
@@ -8060,10 +8060,10 @@
         <v>1</v>
       </c>
       <c r="C545" t="n">
-        <v>11.72895277</v>
+        <v>96.52566735000001</v>
       </c>
       <c r="D545" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="546">
@@ -8071,13 +8071,13 @@
         <v>0</v>
       </c>
       <c r="B546" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C546" t="n">
-        <v>92.64887064</v>
+        <v>8.31211499</v>
       </c>
       <c r="D546" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="547">
@@ -8085,13 +8085,13 @@
         <v>0</v>
       </c>
       <c r="B547" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C547" t="n">
-        <v>132.8952772</v>
+        <v>144.5913758</v>
       </c>
       <c r="D547" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="548">
@@ -8102,21 +8102,21 @@
         <v>1</v>
       </c>
       <c r="C548" t="n">
-        <v>74.05338809</v>
+        <v>59.40041068</v>
       </c>
       <c r="D548" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B549" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C549" t="n">
-        <v>60.25462012</v>
+        <v>7.589322382</v>
       </c>
       <c r="D549" t="b">
         <v>1</v>
@@ -8124,16 +8124,16 @@
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B550" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C550" t="n">
-        <v>34.59548255</v>
+        <v>9.790554415000001</v>
       </c>
       <c r="D550" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="551">
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="B551" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C551" t="n">
-        <v>7.030800821</v>
+        <v>43.4661191</v>
       </c>
       <c r="D551" t="b">
         <v>1</v>
@@ -8152,13 +8152,13 @@
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B552" t="n">
         <v>0</v>
       </c>
       <c r="C552" t="n">
-        <v>80.98562628000001</v>
+        <v>24.83778234</v>
       </c>
       <c r="D552" t="b">
         <v>1</v>
@@ -8172,7 +8172,7 @@
         <v>1</v>
       </c>
       <c r="C553" t="n">
-        <v>19.58110883</v>
+        <v>9.527720738999999</v>
       </c>
       <c r="D553" t="b">
         <v>1</v>
@@ -8180,13 +8180,13 @@
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B554" t="n">
         <v>0</v>
       </c>
       <c r="C554" t="n">
-        <v>7.589322382</v>
+        <v>45.30595483</v>
       </c>
       <c r="D554" t="b">
         <v>1</v>
@@ -8197,24 +8197,24 @@
         <v>0</v>
       </c>
       <c r="B555" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C555" t="n">
-        <v>93.8973306</v>
+        <v>11.03901437</v>
       </c>
       <c r="D555" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B556" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C556" t="n">
-        <v>17.01848049</v>
+        <v>61.79876797</v>
       </c>
       <c r="D556" t="b">
         <v>1</v>
@@ -8222,16 +8222,16 @@
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B557" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C557" t="n">
-        <v>15.34291581</v>
+        <v>21.88090349</v>
       </c>
       <c r="D557" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="558">
@@ -8239,27 +8239,27 @@
         <v>0</v>
       </c>
       <c r="B558" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C558" t="n">
-        <v>35.74537988</v>
+        <v>16.06570842</v>
       </c>
       <c r="D558" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B559" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C559" t="n">
-        <v>3.975359343</v>
+        <v>40.11498973</v>
       </c>
       <c r="D559" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="560">
@@ -8267,13 +8267,13 @@
         <v>0</v>
       </c>
       <c r="B560" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C560" t="n">
-        <v>26.21765914</v>
+        <v>113.8398357</v>
       </c>
       <c r="D560" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="561">
@@ -8281,13 +8281,13 @@
         <v>0</v>
       </c>
       <c r="B561" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C561" t="n">
-        <v>57.62628337</v>
+        <v>9.889117043000001</v>
       </c>
       <c r="D561" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="562">
@@ -8298,10 +8298,10 @@
         <v>1</v>
       </c>
       <c r="C562" t="n">
-        <v>129.2813142</v>
+        <v>8.180698152</v>
       </c>
       <c r="D562" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="563">
@@ -8312,21 +8312,21 @@
         <v>1</v>
       </c>
       <c r="C563" t="n">
-        <v>4.993839836</v>
+        <v>5.749486653</v>
       </c>
       <c r="D563" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B564" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C564" t="n">
-        <v>24.27926078</v>
+        <v>5.453798768</v>
       </c>
       <c r="D564" t="b">
         <v>0</v>
@@ -8334,16 +8334,16 @@
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B565" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C565" t="n">
-        <v>67.84394251000001</v>
+        <v>19.44969199</v>
       </c>
       <c r="D565" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="566">
@@ -8354,7 +8354,7 @@
         <v>1</v>
       </c>
       <c r="C566" t="n">
-        <v>58.21765914</v>
+        <v>19.44969199</v>
       </c>
       <c r="D566" t="b">
         <v>0</v>
@@ -8365,13 +8365,13 @@
         <v>0</v>
       </c>
       <c r="B567" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C567" t="n">
-        <v>49.70841889</v>
+        <v>39.22792608</v>
       </c>
       <c r="D567" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="568">
@@ -8382,7 +8382,7 @@
         <v>1</v>
       </c>
       <c r="C568" t="n">
-        <v>8.410677617999999</v>
+        <v>27.40041068</v>
       </c>
       <c r="D568" t="b">
         <v>0</v>
@@ -8396,24 +8396,24 @@
         <v>1</v>
       </c>
       <c r="C569" t="n">
-        <v>20.56673511</v>
+        <v>55.12936345</v>
       </c>
       <c r="D569" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B570" t="n">
         <v>0</v>
       </c>
       <c r="C570" t="n">
-        <v>24.3449692</v>
+        <v>47.6386037</v>
       </c>
       <c r="D570" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="571">
@@ -8424,7 +8424,7 @@
         <v>0</v>
       </c>
       <c r="C571" t="n">
-        <v>21.15811088</v>
+        <v>73.39630390000001</v>
       </c>
       <c r="D571" t="b">
         <v>0</v>
@@ -8438,7 +8438,7 @@
         <v>1</v>
       </c>
       <c r="C572" t="n">
-        <v>23.45790554</v>
+        <v>58.97330595</v>
       </c>
       <c r="D572" t="b">
         <v>0</v>
@@ -8452,38 +8452,38 @@
         <v>1</v>
       </c>
       <c r="C573" t="n">
-        <v>35.84394251</v>
+        <v>35.38398357</v>
       </c>
       <c r="D573" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B574" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C574" t="n">
-        <v>16.49281314</v>
+        <v>42.48049281</v>
       </c>
       <c r="D574" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B575" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C575" t="n">
-        <v>34.03696099</v>
+        <v>5.092402464</v>
       </c>
       <c r="D575" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="576">
@@ -8491,10 +8491,10 @@
         <v>0</v>
       </c>
       <c r="B576" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C576" t="n">
-        <v>34.49691992</v>
+        <v>20.76386037</v>
       </c>
       <c r="D576" t="b">
         <v>0</v>
@@ -8508,7 +8508,7 @@
         <v>0</v>
       </c>
       <c r="C577" t="n">
-        <v>22.73511294</v>
+        <v>26.15195072</v>
       </c>
       <c r="D577" t="b">
         <v>1</v>
@@ -8519,13 +8519,13 @@
         <v>0</v>
       </c>
       <c r="B578" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C578" t="n">
-        <v>81.64271047</v>
+        <v>12.68172485</v>
       </c>
       <c r="D578" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="579">
@@ -8533,10 +8533,10 @@
         <v>0</v>
       </c>
       <c r="B579" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C579" t="n">
-        <v>128.1314168</v>
+        <v>37.32238193</v>
       </c>
       <c r="D579" t="b">
         <v>0</v>
@@ -8544,16 +8544,16 @@
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B580" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C580" t="n">
-        <v>7.162217659</v>
+        <v>51.08829569</v>
       </c>
       <c r="D580" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="581">
@@ -8564,7 +8564,7 @@
         <v>1</v>
       </c>
       <c r="C581" t="n">
-        <v>115.5482546</v>
+        <v>12.38603696</v>
       </c>
       <c r="D581" t="b">
         <v>0</v>
@@ -8572,16 +8572,16 @@
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B582" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C582" t="n">
-        <v>17.60985626</v>
+        <v>30.68583162</v>
       </c>
       <c r="D582" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="583">
@@ -8589,27 +8589,27 @@
         <v>0</v>
       </c>
       <c r="B583" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C583" t="n">
-        <v>6.800821355</v>
+        <v>166.0780287</v>
       </c>
       <c r="D583" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B584" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C584" t="n">
-        <v>42.18480493</v>
+        <v>2.266940452</v>
       </c>
       <c r="D584" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="585">
@@ -8620,10 +8620,10 @@
         <v>1</v>
       </c>
       <c r="C585" t="n">
-        <v>28.15605749</v>
+        <v>21.48665298</v>
       </c>
       <c r="D585" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="586">
@@ -8634,24 +8634,24 @@
         <v>0</v>
       </c>
       <c r="C586" t="n">
-        <v>51.58110883</v>
+        <v>80.06570842000001</v>
       </c>
       <c r="D586" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B587" t="n">
         <v>0</v>
       </c>
       <c r="C587" t="n">
-        <v>3.811088296</v>
+        <v>52.66529774</v>
       </c>
       <c r="D587" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="588">
@@ -8662,10 +8662,10 @@
         <v>1</v>
       </c>
       <c r="C588" t="n">
-        <v>5.848049281</v>
+        <v>48.45995893</v>
       </c>
       <c r="D588" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="589">
@@ -8676,21 +8676,21 @@
         <v>0</v>
       </c>
       <c r="C589" t="n">
-        <v>15.60574949</v>
+        <v>18.49691992</v>
       </c>
       <c r="D589" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B590" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C590" t="n">
-        <v>19.05544148</v>
+        <v>21.88090349</v>
       </c>
       <c r="D590" t="b">
         <v>0</v>
@@ -8701,10 +8701,10 @@
         <v>0</v>
       </c>
       <c r="B591" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C591" t="n">
-        <v>73.13347023</v>
+        <v>1.839835729</v>
       </c>
       <c r="D591" t="b">
         <v>0</v>
@@ -8718,7 +8718,7 @@
         <v>0</v>
       </c>
       <c r="C592" t="n">
-        <v>89.00205339</v>
+        <v>8.640657084000001</v>
       </c>
       <c r="D592" t="b">
         <v>1</v>
@@ -8726,16 +8726,16 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B593" t="n">
         <v>0</v>
       </c>
       <c r="C593" t="n">
-        <v>79.80287473999999</v>
+        <v>22.07802875</v>
       </c>
       <c r="D593" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="594">
@@ -8746,10 +8746,10 @@
         <v>1</v>
       </c>
       <c r="C594" t="n">
-        <v>10.51334702</v>
+        <v>13.07597536</v>
       </c>
       <c r="D594" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="595">
@@ -8757,10 +8757,10 @@
         <v>0</v>
       </c>
       <c r="B595" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C595" t="n">
-        <v>9.034907598</v>
+        <v>4.76386037</v>
       </c>
       <c r="D595" t="b">
         <v>0</v>
@@ -8774,7 +8774,7 @@
         <v>1</v>
       </c>
       <c r="C596" t="n">
-        <v>63.54004107</v>
+        <v>46.78439425</v>
       </c>
       <c r="D596" t="b">
         <v>1</v>
@@ -8788,7 +8788,7 @@
         <v>1</v>
       </c>
       <c r="C597" t="n">
-        <v>10.84188912</v>
+        <v>57.82340862</v>
       </c>
       <c r="D597" t="b">
         <v>1</v>
@@ -8802,7 +8802,7 @@
         <v>1</v>
       </c>
       <c r="C598" t="n">
-        <v>27.4661191</v>
+        <v>22.66940452</v>
       </c>
       <c r="D598" t="b">
         <v>0</v>
@@ -8810,30 +8810,30 @@
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B599" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C599" t="n">
-        <v>8.87063655</v>
+        <v>28.81314168</v>
       </c>
       <c r="D599" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B600" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C600" t="n">
-        <v>128.0657084</v>
+        <v>8.180698152</v>
       </c>
       <c r="D600" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="601">
@@ -8841,13 +8841,13 @@
         <v>0</v>
       </c>
       <c r="B601" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C601" t="n">
-        <v>32.88706366</v>
+        <v>96.72279261</v>
       </c>
       <c r="D601" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="602">
@@ -8858,21 +8858,21 @@
         <v>0</v>
       </c>
       <c r="C602" t="n">
-        <v>15.93429158</v>
+        <v>5.388090349</v>
       </c>
       <c r="D602" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B603" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C603" t="n">
-        <v>60.78028747</v>
+        <v>15.11293634</v>
       </c>
       <c r="D603" t="b">
         <v>0</v>
@@ -8880,13 +8880,13 @@
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B604" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C604" t="n">
-        <v>5.650924025</v>
+        <v>81.83983573</v>
       </c>
       <c r="D604" t="b">
         <v>1</v>
@@ -8894,13 +8894,13 @@
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B605" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C605" t="n">
-        <v>9.790554415000001</v>
+        <v>33.57700205</v>
       </c>
       <c r="D605" t="b">
         <v>1</v>
@@ -8914,10 +8914,10 @@
         <v>1</v>
       </c>
       <c r="C606" t="n">
-        <v>18.7926078</v>
+        <v>6.143737166</v>
       </c>
       <c r="D606" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="607">
@@ -8928,10 +8928,10 @@
         <v>1</v>
       </c>
       <c r="C607" t="n">
-        <v>36.73100616</v>
+        <v>133.9137577</v>
       </c>
       <c r="D607" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="608">
@@ -8942,7 +8942,7 @@
         <v>1</v>
       </c>
       <c r="C608" t="n">
-        <v>13.17453799</v>
+        <v>52.50102669</v>
       </c>
       <c r="D608" t="b">
         <v>1</v>
@@ -8956,7 +8956,7 @@
         <v>1</v>
       </c>
       <c r="C609" t="n">
-        <v>94.12731006</v>
+        <v>31.50718686</v>
       </c>
       <c r="D609" t="b">
         <v>0</v>
@@ -8964,27 +8964,27 @@
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B610" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C610" t="n">
-        <v>27.56468172</v>
+        <v>11.69609856</v>
       </c>
       <c r="D610" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B611" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C611" t="n">
-        <v>53.19096509</v>
+        <v>37.12525667</v>
       </c>
       <c r="D611" t="b">
         <v>1</v>
@@ -8992,13 +8992,13 @@
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B612" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C612" t="n">
-        <v>1.80698152</v>
+        <v>6.866529774</v>
       </c>
       <c r="D612" t="b">
         <v>0</v>
@@ -9009,41 +9009,41 @@
         <v>0</v>
       </c>
       <c r="B613" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C613" t="n">
-        <v>18.56262834</v>
+        <v>29.01026694</v>
       </c>
       <c r="D613" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B614" t="n">
         <v>1</v>
       </c>
       <c r="C614" t="n">
-        <v>3.416837782</v>
+        <v>16.75564682</v>
       </c>
       <c r="D614" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B615" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C615" t="n">
-        <v>26.94045175</v>
+        <v>73.82340862</v>
       </c>
       <c r="D615" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="616">
@@ -9054,7 +9054,7 @@
         <v>1</v>
       </c>
       <c r="C616" t="n">
-        <v>45.07597536</v>
+        <v>57.52772074</v>
       </c>
       <c r="D616" t="b">
         <v>0</v>
@@ -9068,10 +9068,10 @@
         <v>0</v>
       </c>
       <c r="C617" t="n">
-        <v>49.7412731</v>
+        <v>64.29568789</v>
       </c>
       <c r="D617" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="618">
@@ -9082,10 +9082,10 @@
         <v>1</v>
       </c>
       <c r="C618" t="n">
-        <v>4.960985626</v>
+        <v>7.162217659</v>
       </c>
       <c r="D618" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="619">
@@ -9096,7 +9096,7 @@
         <v>1</v>
       </c>
       <c r="C619" t="n">
-        <v>41.69199179</v>
+        <v>23.68788501</v>
       </c>
       <c r="D619" t="b">
         <v>1</v>
@@ -9107,10 +9107,10 @@
         <v>0</v>
       </c>
       <c r="B620" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C620" t="n">
-        <v>54.07802875</v>
+        <v>45.5687885</v>
       </c>
       <c r="D620" t="b">
         <v>1</v>
@@ -9121,13 +9121,13 @@
         <v>0</v>
       </c>
       <c r="B621" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C621" t="n">
-        <v>0.492813142</v>
+        <v>13.66735113</v>
       </c>
       <c r="D621" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="622">
@@ -9138,10 +9138,10 @@
         <v>1</v>
       </c>
       <c r="C622" t="n">
-        <v>26.67761807</v>
+        <v>51.08829569</v>
       </c>
       <c r="D622" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="623">
@@ -9149,13 +9149,13 @@
         <v>0</v>
       </c>
       <c r="B623" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C623" t="n">
-        <v>25.98767967</v>
+        <v>140.2217659</v>
       </c>
       <c r="D623" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="624">
@@ -9166,7 +9166,7 @@
         <v>1</v>
       </c>
       <c r="C624" t="n">
-        <v>3.121149897</v>
+        <v>0.492813142</v>
       </c>
       <c r="D624" t="b">
         <v>0</v>
@@ -9177,13 +9177,13 @@
         <v>0</v>
       </c>
       <c r="B625" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C625" t="n">
-        <v>6.078028747</v>
+        <v>47.96714579</v>
       </c>
       <c r="D625" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="626">
@@ -9191,24 +9191,24 @@
         <v>0</v>
       </c>
       <c r="B626" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C626" t="n">
-        <v>11.79466119</v>
+        <v>55.78644764</v>
       </c>
       <c r="D626" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B627" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C627" t="n">
-        <v>7.852156057</v>
+        <v>38.89938398</v>
       </c>
       <c r="D627" t="b">
         <v>0</v>
@@ -9222,7 +9222,7 @@
         <v>1</v>
       </c>
       <c r="C628" t="n">
-        <v>8.607802875000001</v>
+        <v>114.8583162</v>
       </c>
       <c r="D628" t="b">
         <v>1</v>
@@ -9236,7 +9236,7 @@
         <v>0</v>
       </c>
       <c r="C629" t="n">
-        <v>12.78028747</v>
+        <v>26.11909651</v>
       </c>
       <c r="D629" t="b">
         <v>1</v>
@@ -9247,10 +9247,10 @@
         <v>0</v>
       </c>
       <c r="B630" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C630" t="n">
-        <v>22.73511294</v>
+        <v>87.68788501</v>
       </c>
       <c r="D630" t="b">
         <v>1</v>
@@ -9261,10 +9261,10 @@
         <v>0</v>
       </c>
       <c r="B631" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C631" t="n">
-        <v>1.347022587</v>
+        <v>42.61190965</v>
       </c>
       <c r="D631" t="b">
         <v>0</v>
@@ -9278,7 +9278,7 @@
         <v>1</v>
       </c>
       <c r="C632" t="n">
-        <v>2.39835729</v>
+        <v>5.289527721</v>
       </c>
       <c r="D632" t="b">
         <v>0</v>
@@ -9292,10 +9292,10 @@
         <v>1</v>
       </c>
       <c r="C633" t="n">
-        <v>15.14579055</v>
+        <v>94.78439425000001</v>
       </c>
       <c r="D633" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="634">
@@ -9303,10 +9303,10 @@
         <v>0</v>
       </c>
       <c r="B634" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C634" t="n">
-        <v>23.9835729</v>
+        <v>86.83367556</v>
       </c>
       <c r="D634" t="b">
         <v>1</v>
@@ -9320,7 +9320,7 @@
         <v>1</v>
       </c>
       <c r="C635" t="n">
-        <v>23.95071869</v>
+        <v>2.792607803</v>
       </c>
       <c r="D635" t="b">
         <v>1</v>
@@ -9334,10 +9334,10 @@
         <v>1</v>
       </c>
       <c r="C636" t="n">
-        <v>13.73305955</v>
+        <v>13.33880903</v>
       </c>
       <c r="D636" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="637">
@@ -9348,7 +9348,7 @@
         <v>1</v>
       </c>
       <c r="C637" t="n">
-        <v>33.57700205</v>
+        <v>16.65708419</v>
       </c>
       <c r="D637" t="b">
         <v>0</v>
@@ -9362,7 +9362,7 @@
         <v>1</v>
       </c>
       <c r="C638" t="n">
-        <v>34.56262834</v>
+        <v>12.02464066</v>
       </c>
       <c r="D638" t="b">
         <v>1</v>
@@ -9376,10 +9376,10 @@
         <v>1</v>
       </c>
       <c r="C639" t="n">
-        <v>7.12936345</v>
+        <v>8.936344969</v>
       </c>
       <c r="D639" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="640">
@@ -9387,13 +9387,13 @@
         <v>0</v>
       </c>
       <c r="B640" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C640" t="n">
-        <v>70.93223819000001</v>
+        <v>23.52361396</v>
       </c>
       <c r="D640" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="641">
@@ -9404,10 +9404,10 @@
         <v>1</v>
       </c>
       <c r="C641" t="n">
-        <v>123.0718686</v>
+        <v>18.16837782</v>
       </c>
       <c r="D641" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="642">
@@ -9418,10 +9418,10 @@
         <v>1</v>
       </c>
       <c r="C642" t="n">
-        <v>48.09856263</v>
+        <v>23.2936345</v>
       </c>
       <c r="D642" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="643">
@@ -9432,10 +9432,10 @@
         <v>1</v>
       </c>
       <c r="C643" t="n">
-        <v>44.48459959</v>
+        <v>23.45790554</v>
       </c>
       <c r="D643" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="644">
@@ -9446,7 +9446,7 @@
         <v>0</v>
       </c>
       <c r="C644" t="n">
-        <v>36.59958932</v>
+        <v>11.8275154</v>
       </c>
       <c r="D644" t="b">
         <v>0</v>
@@ -9457,10 +9457,10 @@
         <v>0</v>
       </c>
       <c r="B645" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C645" t="n">
-        <v>12.05749487</v>
+        <v>45.37166324</v>
       </c>
       <c r="D645" t="b">
         <v>1</v>
@@ -9474,7 +9474,7 @@
         <v>1</v>
       </c>
       <c r="C646" t="n">
-        <v>103.5893224</v>
+        <v>63.70431211</v>
       </c>
       <c r="D646" t="b">
         <v>0</v>
@@ -9485,10 +9485,10 @@
         <v>0</v>
       </c>
       <c r="B647" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C647" t="n">
-        <v>82.7926078</v>
+        <v>30.35728953</v>
       </c>
       <c r="D647" t="b">
         <v>0</v>
@@ -9502,21 +9502,21 @@
         <v>1</v>
       </c>
       <c r="C648" t="n">
-        <v>101.5195072</v>
+        <v>8.180698152</v>
       </c>
       <c r="D648" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B649" t="n">
         <v>0</v>
       </c>
       <c r="C649" t="n">
-        <v>11.56468172</v>
+        <v>95.96714579</v>
       </c>
       <c r="D649" t="b">
         <v>0</v>
@@ -9527,10 +9527,10 @@
         <v>1</v>
       </c>
       <c r="B650" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C650" t="n">
-        <v>7.950718686</v>
+        <v>48.19712526</v>
       </c>
       <c r="D650" t="b">
         <v>0</v>
@@ -9541,10 +9541,10 @@
         <v>0</v>
       </c>
       <c r="B651" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C651" t="n">
-        <v>46.9486653</v>
+        <v>24.27926078</v>
       </c>
       <c r="D651" t="b">
         <v>0</v>
@@ -9555,27 +9555,27 @@
         <v>0</v>
       </c>
       <c r="B652" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C652" t="n">
-        <v>65.37987680000001</v>
+        <v>26.21765914</v>
       </c>
       <c r="D652" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B653" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C653" t="n">
-        <v>44.02464066</v>
+        <v>48.62422998</v>
       </c>
       <c r="D653" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="654">
@@ -9586,7 +9586,7 @@
         <v>0</v>
       </c>
       <c r="C654" t="n">
-        <v>12.25462012</v>
+        <v>15.17864476</v>
       </c>
       <c r="D654" t="b">
         <v>0</v>
@@ -9600,7 +9600,7 @@
         <v>1</v>
       </c>
       <c r="C655" t="n">
-        <v>39.68788501</v>
+        <v>109.2402464</v>
       </c>
       <c r="D655" t="b">
         <v>0</v>
@@ -9608,13 +9608,13 @@
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B656" t="n">
         <v>1</v>
       </c>
       <c r="C656" t="n">
-        <v>50.23408624</v>
+        <v>132.4024641</v>
       </c>
       <c r="D656" t="b">
         <v>0</v>
@@ -9622,44 +9622,44 @@
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B657" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C657" t="n">
-        <v>13.40451745</v>
+        <v>99.77823409</v>
       </c>
       <c r="D657" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B658" t="n">
         <v>0</v>
       </c>
       <c r="C658" t="n">
-        <v>13.40451745</v>
+        <v>24.27926078</v>
       </c>
       <c r="D658" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B659" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C659" t="n">
-        <v>9.067761807</v>
+        <v>10.48049281</v>
       </c>
       <c r="D659" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="660">
@@ -9670,7 +9670,7 @@
         <v>1</v>
       </c>
       <c r="C660" t="n">
-        <v>40.31211499</v>
+        <v>23.12936345</v>
       </c>
       <c r="D660" t="b">
         <v>0</v>
@@ -9684,10 +9684,10 @@
         <v>0</v>
       </c>
       <c r="C661" t="n">
-        <v>16.06570842</v>
+        <v>36.96098563</v>
       </c>
       <c r="D661" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="662">
@@ -9695,13 +9695,13 @@
         <v>0</v>
       </c>
       <c r="B662" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C662" t="n">
-        <v>38.86652977</v>
+        <v>42.0862423</v>
       </c>
       <c r="D662" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="663">
@@ -9712,7 +9712,7 @@
         <v>1</v>
       </c>
       <c r="C663" t="n">
-        <v>22.63655031</v>
+        <v>26.94045175</v>
       </c>
       <c r="D663" t="b">
         <v>1</v>
@@ -9720,44 +9720,44 @@
     </row>
     <row r="664">
       <c r="A664" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B664" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C664" t="n">
-        <v>9.199178645</v>
+        <v>9.330595483</v>
       </c>
       <c r="D664" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B665" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C665" t="n">
-        <v>40.37782341</v>
+        <v>32.52566735</v>
       </c>
       <c r="D665" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B666" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C666" t="n">
-        <v>42.38193018</v>
+        <v>4.041067762</v>
       </c>
       <c r="D666" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="667">
@@ -9765,10 +9765,10 @@
         <v>0</v>
       </c>
       <c r="B667" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C667" t="n">
-        <v>61.73305955</v>
+        <v>35.77823409</v>
       </c>
       <c r="D667" t="b">
         <v>1</v>
@@ -9776,16 +9776,16 @@
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B668" t="n">
         <v>0</v>
       </c>
       <c r="C668" t="n">
-        <v>46.35728953</v>
+        <v>103.7207392</v>
       </c>
       <c r="D668" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="669">
@@ -9796,7 +9796,7 @@
         <v>1</v>
       </c>
       <c r="C669" t="n">
-        <v>3.975359343</v>
+        <v>34.95687885</v>
       </c>
       <c r="D669" t="b">
         <v>1</v>
@@ -9804,13 +9804,13 @@
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B670" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C670" t="n">
-        <v>51.31827515</v>
+        <v>33.97125257</v>
       </c>
       <c r="D670" t="b">
         <v>0</v>
@@ -9818,27 +9818,27 @@
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B671" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C671" t="n">
-        <v>27.92607803</v>
+        <v>52.862423</v>
       </c>
       <c r="D671" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B672" t="n">
         <v>0</v>
       </c>
       <c r="C672" t="n">
-        <v>78.68583162</v>
+        <v>6.176591376</v>
       </c>
       <c r="D672" t="b">
         <v>1</v>
@@ -9849,10 +9849,10 @@
         <v>0</v>
       </c>
       <c r="B673" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C673" t="n">
-        <v>61.07597536</v>
+        <v>53.09240246</v>
       </c>
       <c r="D673" t="b">
         <v>0</v>
@@ -9866,10 +9866,10 @@
         <v>0</v>
       </c>
       <c r="C674" t="n">
-        <v>79.54004107</v>
+        <v>103.3921971</v>
       </c>
       <c r="D674" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="675">
@@ -9880,10 +9880,10 @@
         <v>1</v>
       </c>
       <c r="C675" t="n">
-        <v>166.275154</v>
+        <v>1.149897331</v>
       </c>
       <c r="D675" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="676">
@@ -9894,7 +9894,7 @@
         <v>1</v>
       </c>
       <c r="C676" t="n">
-        <v>3.811088296</v>
+        <v>89.36344969</v>
       </c>
       <c r="D676" t="b">
         <v>1</v>
@@ -9902,16 +9902,16 @@
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B677" t="n">
         <v>1</v>
       </c>
       <c r="C677" t="n">
-        <v>34.56262834</v>
+        <v>2.102669405</v>
       </c>
       <c r="D677" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="678">
@@ -9919,27 +9919,13 @@
         <v>0</v>
       </c>
       <c r="B678" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C678" t="n">
-        <v>68.27104722999999</v>
+        <v>118.8008214</v>
       </c>
       <c r="D678" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="679">
-      <c r="A679" t="n">
-        <v>1</v>
-      </c>
-      <c r="B679" t="n">
-        <v>0</v>
-      </c>
-      <c r="C679" t="n">
-        <v>5.420944559</v>
-      </c>
-      <c r="D679" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/df_train_transfored.xlsx
+++ b/df_train_transfored.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D678"/>
+  <dimension ref="A1:D679"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -609,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="B13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C13" t="n">
         <v>64.75564682</v>
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="B30" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C30" t="n">
         <v>12.68172485</v>
@@ -1337,7 +1337,7 @@
         <v>0</v>
       </c>
       <c r="B65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C65" t="n">
         <v>96</v>
@@ -1519,7 +1519,7 @@
         <v>0</v>
       </c>
       <c r="B78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C78" t="n">
         <v>38.70225873</v>
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C100" t="n">
         <v>51.94250513</v>
@@ -2275,7 +2275,7 @@
         <v>0</v>
       </c>
       <c r="B132" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C132" t="n">
         <v>39.72073922</v>
@@ -2499,7 +2499,7 @@
         <v>0</v>
       </c>
       <c r="B148" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C148" t="n">
         <v>11.95893224</v>
@@ -2821,7 +2821,7 @@
         <v>0</v>
       </c>
       <c r="B171" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C171" t="n">
         <v>5.092402464</v>
@@ -3059,7 +3059,7 @@
         <v>0</v>
       </c>
       <c r="B188" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C188" t="n">
         <v>25.33059548</v>
@@ -3451,7 +3451,7 @@
         <v>1</v>
       </c>
       <c r="B216" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C216" t="n">
         <v>2.135523614</v>
@@ -3574,16 +3574,16 @@
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B225" t="n">
         <v>0</v>
       </c>
       <c r="C225" t="n">
-        <v>5.650924025</v>
+        <v>120.4435318</v>
       </c>
       <c r="D225" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="226">
@@ -3591,13 +3591,13 @@
         <v>0</v>
       </c>
       <c r="B226" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C226" t="n">
-        <v>81.64271047</v>
+        <v>5.782340862</v>
       </c>
       <c r="D226" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="227">
@@ -3608,10 +3608,10 @@
         <v>1</v>
       </c>
       <c r="C227" t="n">
-        <v>138.9404517</v>
+        <v>8.772073922000001</v>
       </c>
       <c r="D227" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="228">
@@ -3622,10 +3622,10 @@
         <v>0</v>
       </c>
       <c r="C228" t="n">
-        <v>32.49281314</v>
+        <v>5.650924025</v>
       </c>
       <c r="D228" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="229">
@@ -3636,7 +3636,7 @@
         <v>1</v>
       </c>
       <c r="C229" t="n">
-        <v>5.815195072</v>
+        <v>13.86447639</v>
       </c>
       <c r="D229" t="b">
         <v>1</v>
@@ -3647,13 +3647,13 @@
         <v>0</v>
       </c>
       <c r="B230" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C230" t="n">
-        <v>19.84394251</v>
+        <v>81.64271047</v>
       </c>
       <c r="D230" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="231">
@@ -3664,10 +3664,10 @@
         <v>1</v>
       </c>
       <c r="C231" t="n">
-        <v>6.669404517</v>
+        <v>138.9404517</v>
       </c>
       <c r="D231" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="232">
@@ -3678,7 +3678,7 @@
         <v>0</v>
       </c>
       <c r="C232" t="n">
-        <v>49.31416838</v>
+        <v>6.176591376</v>
       </c>
       <c r="D232" t="b">
         <v>1</v>
@@ -3692,10 +3692,10 @@
         <v>1</v>
       </c>
       <c r="C233" t="n">
-        <v>14.98151951</v>
+        <v>7.227926078</v>
       </c>
       <c r="D233" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="234">
@@ -3706,7 +3706,7 @@
         <v>1</v>
       </c>
       <c r="C234" t="n">
-        <v>16.42710472</v>
+        <v>54.07802875</v>
       </c>
       <c r="D234" t="b">
         <v>1</v>
@@ -3714,27 +3714,27 @@
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B235" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C235" t="n">
-        <v>52.73100616</v>
+        <v>2.694045175</v>
       </c>
       <c r="D235" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B236" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C236" t="n">
-        <v>27.36755647</v>
+        <v>18.33264887</v>
       </c>
       <c r="D236" t="b">
         <v>1</v>
@@ -3748,7 +3748,7 @@
         <v>1</v>
       </c>
       <c r="C237" t="n">
-        <v>50.98973306</v>
+        <v>89.36344969</v>
       </c>
       <c r="D237" t="b">
         <v>1</v>
@@ -3756,13 +3756,13 @@
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B238" t="n">
         <v>0</v>
       </c>
       <c r="C238" t="n">
-        <v>32.85420945</v>
+        <v>48.45995893</v>
       </c>
       <c r="D238" t="b">
         <v>1</v>
@@ -3770,30 +3770,30 @@
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B239" t="n">
         <v>0</v>
       </c>
       <c r="C239" t="n">
-        <v>70.93223819000001</v>
+        <v>1.18275154</v>
       </c>
       <c r="D239" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C240" t="n">
-        <v>11.49897331</v>
+        <v>3.778234086</v>
       </c>
       <c r="D240" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="241">
@@ -3804,21 +3804,21 @@
         <v>1</v>
       </c>
       <c r="C241" t="n">
-        <v>70.83367556</v>
+        <v>76.68172484999999</v>
       </c>
       <c r="D241" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B242" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C242" t="n">
-        <v>35.28542094</v>
+        <v>9.790554415000001</v>
       </c>
       <c r="D242" t="b">
         <v>1</v>
@@ -3826,13 +3826,13 @@
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B243" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C243" t="n">
-        <v>45.30595483</v>
+        <v>7.030800821</v>
       </c>
       <c r="D243" t="b">
         <v>1</v>
@@ -3840,16 +3840,16 @@
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B244" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C244" t="n">
-        <v>23.6550308</v>
+        <v>29.96303901</v>
       </c>
       <c r="D244" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="245">
@@ -3857,13 +3857,13 @@
         <v>0</v>
       </c>
       <c r="B245" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C245" t="n">
-        <v>3.482546201</v>
+        <v>23.9835729</v>
       </c>
       <c r="D245" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="246">
@@ -3871,10 +3871,10 @@
         <v>0</v>
       </c>
       <c r="B246" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C246" t="n">
-        <v>40.3449692</v>
+        <v>22.24229979</v>
       </c>
       <c r="D246" t="b">
         <v>1</v>
@@ -3882,13 +3882,13 @@
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C247" t="n">
-        <v>2.759753593</v>
+        <v>10.90759754</v>
       </c>
       <c r="D247" t="b">
         <v>1</v>
@@ -3899,13 +3899,13 @@
         <v>0</v>
       </c>
       <c r="B248" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C248" t="n">
-        <v>45.30595483</v>
+        <v>27.86036961</v>
       </c>
       <c r="D248" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="249">
@@ -3916,10 +3916,10 @@
         <v>1</v>
       </c>
       <c r="C249" t="n">
-        <v>9.100616016</v>
+        <v>2.234086242</v>
       </c>
       <c r="D249" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="250">
@@ -3930,10 +3930,10 @@
         <v>1</v>
       </c>
       <c r="C250" t="n">
-        <v>11.23613963</v>
+        <v>10.11909651</v>
       </c>
       <c r="D250" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="251">
@@ -3944,7 +3944,7 @@
         <v>1</v>
       </c>
       <c r="C251" t="n">
-        <v>5.848049281</v>
+        <v>73.29774127</v>
       </c>
       <c r="D251" t="b">
         <v>1</v>
@@ -3958,10 +3958,10 @@
         <v>1</v>
       </c>
       <c r="C252" t="n">
-        <v>18.49691992</v>
+        <v>24.24640657</v>
       </c>
       <c r="D252" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="253">
@@ -3969,10 +3969,10 @@
         <v>0</v>
       </c>
       <c r="B253" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C253" t="n">
-        <v>8.410677617999999</v>
+        <v>28.35318275</v>
       </c>
       <c r="D253" t="b">
         <v>1</v>
@@ -3986,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="C254" t="n">
-        <v>59.99178645</v>
+        <v>96.65708419000001</v>
       </c>
       <c r="D254" t="b">
         <v>0</v>
@@ -3994,16 +3994,16 @@
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B255" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C255" t="n">
-        <v>58.94045175</v>
+        <v>9.790554415000001</v>
       </c>
       <c r="D255" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="256">
@@ -4011,10 +4011,10 @@
         <v>0</v>
       </c>
       <c r="B256" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C256" t="n">
-        <v>17.11704312</v>
+        <v>19.51540041</v>
       </c>
       <c r="D256" t="b">
         <v>0</v>
@@ -4025,13 +4025,13 @@
         <v>0</v>
       </c>
       <c r="B257" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C257" t="n">
-        <v>81.24845996000001</v>
+        <v>25.23203285</v>
       </c>
       <c r="D257" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="258">
@@ -4042,24 +4042,24 @@
         <v>1</v>
       </c>
       <c r="C258" t="n">
-        <v>50.29979466</v>
+        <v>60.94455852</v>
       </c>
       <c r="D258" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C259" t="n">
-        <v>7.852156057</v>
+        <v>59.20328542</v>
       </c>
       <c r="D259" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="260">
@@ -4067,10 +4067,10 @@
         <v>0</v>
       </c>
       <c r="B260" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C260" t="n">
-        <v>23.9835729</v>
+        <v>142.4558522</v>
       </c>
       <c r="D260" t="b">
         <v>1</v>
@@ -4078,13 +4078,13 @@
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B261" t="n">
         <v>0</v>
       </c>
       <c r="C261" t="n">
-        <v>3.449691992</v>
+        <v>23.9835729</v>
       </c>
       <c r="D261" t="b">
         <v>1</v>
@@ -4095,13 +4095,13 @@
         <v>0</v>
       </c>
       <c r="B262" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C262" t="n">
-        <v>110.0287474</v>
+        <v>86.83367556</v>
       </c>
       <c r="D262" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="263">
@@ -4109,10 +4109,10 @@
         <v>0</v>
       </c>
       <c r="B263" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C263" t="n">
-        <v>11.53182752</v>
+        <v>34.29979466</v>
       </c>
       <c r="D263" t="b">
         <v>0</v>
@@ -4126,7 +4126,7 @@
         <v>1</v>
       </c>
       <c r="C264" t="n">
-        <v>10.94045175</v>
+        <v>23.55646817</v>
       </c>
       <c r="D264" t="b">
         <v>1</v>
@@ -4140,10 +4140,10 @@
         <v>1</v>
       </c>
       <c r="C265" t="n">
-        <v>3.975359343</v>
+        <v>10.51334702</v>
       </c>
       <c r="D265" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="266">
@@ -4154,10 +4154,10 @@
         <v>1</v>
       </c>
       <c r="C266" t="n">
-        <v>112.788501</v>
+        <v>19.08829569</v>
       </c>
       <c r="D266" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="267">
@@ -4168,7 +4168,7 @@
         <v>1</v>
       </c>
       <c r="C267" t="n">
-        <v>8.772073922000001</v>
+        <v>44.55030801</v>
       </c>
       <c r="D267" t="b">
         <v>0</v>
@@ -4182,10 +4182,10 @@
         <v>1</v>
       </c>
       <c r="C268" t="n">
-        <v>39.88501027</v>
+        <v>50.72689938</v>
       </c>
       <c r="D268" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="269">
@@ -4193,10 +4193,10 @@
         <v>0</v>
       </c>
       <c r="B269" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C269" t="n">
-        <v>16.95277207</v>
+        <v>47.21149897</v>
       </c>
       <c r="D269" t="b">
         <v>0</v>
@@ -4210,10 +4210,10 @@
         <v>1</v>
       </c>
       <c r="C270" t="n">
-        <v>3.975359343</v>
+        <v>10.51334702</v>
       </c>
       <c r="D270" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="271">
@@ -4221,10 +4221,10 @@
         <v>0</v>
       </c>
       <c r="B271" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C271" t="n">
-        <v>14.45585216</v>
+        <v>90.15195072</v>
       </c>
       <c r="D271" t="b">
         <v>0</v>
@@ -4238,10 +4238,10 @@
         <v>1</v>
       </c>
       <c r="C272" t="n">
-        <v>32.45995893</v>
+        <v>72.41067762</v>
       </c>
       <c r="D272" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="273">
@@ -4252,7 +4252,7 @@
         <v>1</v>
       </c>
       <c r="C273" t="n">
-        <v>10.7761807</v>
+        <v>133.8809035</v>
       </c>
       <c r="D273" t="b">
         <v>1</v>
@@ -4266,10 +4266,10 @@
         <v>1</v>
       </c>
       <c r="C274" t="n">
-        <v>26.0862423</v>
+        <v>94.81724846</v>
       </c>
       <c r="D274" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275">
@@ -4280,7 +4280,7 @@
         <v>1</v>
       </c>
       <c r="C275" t="n">
-        <v>144.7556468</v>
+        <v>16.62422998</v>
       </c>
       <c r="D275" t="b">
         <v>0</v>
@@ -4288,16 +4288,16 @@
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B276" t="n">
         <v>1</v>
       </c>
       <c r="C276" t="n">
-        <v>10.02053388</v>
+        <v>19.87679671</v>
       </c>
       <c r="D276" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="277">
@@ -4305,10 +4305,10 @@
         <v>0</v>
       </c>
       <c r="B277" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C277" t="n">
-        <v>123.6960986</v>
+        <v>52.79671458</v>
       </c>
       <c r="D277" t="b">
         <v>0</v>
@@ -4319,13 +4319,13 @@
         <v>0</v>
       </c>
       <c r="B278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C278" t="n">
-        <v>20.92813142</v>
+        <v>30.71868583</v>
       </c>
       <c r="D278" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="279">
@@ -4336,10 +4336,10 @@
         <v>1</v>
       </c>
       <c r="C279" t="n">
-        <v>45.37166324</v>
+        <v>16.62422998</v>
       </c>
       <c r="D279" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="280">
@@ -4350,10 +4350,10 @@
         <v>1</v>
       </c>
       <c r="C280" t="n">
-        <v>8.344969198999999</v>
+        <v>7.030800821</v>
       </c>
       <c r="D280" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="281">
@@ -4364,7 +4364,7 @@
         <v>0</v>
       </c>
       <c r="C281" t="n">
-        <v>14.48870637</v>
+        <v>17.08418891</v>
       </c>
       <c r="D281" t="b">
         <v>0</v>
@@ -4372,13 +4372,13 @@
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B282" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C282" t="n">
-        <v>33.67556468</v>
+        <v>2.825462012</v>
       </c>
       <c r="D282" t="b">
         <v>0</v>
@@ -4389,10 +4389,10 @@
         <v>0</v>
       </c>
       <c r="B283" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C283" t="n">
-        <v>14.48870637</v>
+        <v>38.01232033</v>
       </c>
       <c r="D283" t="b">
         <v>0</v>
@@ -4400,16 +4400,16 @@
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B284" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C284" t="n">
-        <v>15.14579055</v>
+        <v>23.52361396</v>
       </c>
       <c r="D284" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="285">
@@ -4417,27 +4417,27 @@
         <v>0</v>
       </c>
       <c r="B285" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C285" t="n">
-        <v>33.93839836</v>
+        <v>59.76180698</v>
       </c>
       <c r="D285" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B286" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C286" t="n">
-        <v>33.28131417</v>
+        <v>42.94045175</v>
       </c>
       <c r="D286" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="287">
@@ -4448,10 +4448,10 @@
         <v>1</v>
       </c>
       <c r="C287" t="n">
-        <v>16.65708419</v>
+        <v>73.29774127</v>
       </c>
       <c r="D287" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="288">
@@ -4462,7 +4462,7 @@
         <v>0</v>
       </c>
       <c r="C288" t="n">
-        <v>22.73511294</v>
+        <v>1.412731006</v>
       </c>
       <c r="D288" t="b">
         <v>1</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="B289" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C289" t="n">
-        <v>12.8788501</v>
+        <v>45.30595483</v>
       </c>
       <c r="D289" t="b">
         <v>1</v>
@@ -4487,13 +4487,13 @@
         <v>0</v>
       </c>
       <c r="B290" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C290" t="n">
-        <v>27.56468172</v>
+        <v>130.9897331</v>
       </c>
       <c r="D290" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="291">
@@ -4501,10 +4501,10 @@
         <v>0</v>
       </c>
       <c r="B291" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C291" t="n">
-        <v>42.57905544</v>
+        <v>29.8973306</v>
       </c>
       <c r="D291" t="b">
         <v>0</v>
@@ -4512,27 +4512,27 @@
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B292" t="n">
         <v>0</v>
       </c>
       <c r="C292" t="n">
-        <v>22.24229979</v>
+        <v>70.93223819000001</v>
       </c>
       <c r="D292" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B293" t="n">
         <v>1</v>
       </c>
       <c r="C293" t="n">
-        <v>4.501026694</v>
+        <v>19.1211499</v>
       </c>
       <c r="D293" t="b">
         <v>0</v>
@@ -4546,7 +4546,7 @@
         <v>1</v>
       </c>
       <c r="C294" t="n">
-        <v>12.78028747</v>
+        <v>25.06776181</v>
       </c>
       <c r="D294" t="b">
         <v>1</v>
@@ -4557,38 +4557,38 @@
         <v>0</v>
       </c>
       <c r="B295" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C295" t="n">
-        <v>79.86858316</v>
+        <v>20.46817248</v>
       </c>
       <c r="D295" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B296" t="n">
         <v>0</v>
       </c>
       <c r="C296" t="n">
-        <v>14.06160164</v>
+        <v>16</v>
       </c>
       <c r="D296" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C297" t="n">
-        <v>16.95277207</v>
+        <v>32</v>
       </c>
       <c r="D297" t="b">
         <v>0</v>
@@ -4602,10 +4602,10 @@
         <v>1</v>
       </c>
       <c r="C298" t="n">
-        <v>5.026694045</v>
+        <v>7.852156057</v>
       </c>
       <c r="D298" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="299">
@@ -4616,49 +4616,49 @@
         <v>1</v>
       </c>
       <c r="C299" t="n">
-        <v>19.74537988</v>
+        <v>28.35318275</v>
       </c>
       <c r="D299" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B300" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C300" t="n">
-        <v>48.19712526</v>
+        <v>53.81519507</v>
       </c>
       <c r="D300" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B301" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C301" t="n">
-        <v>10.61190965</v>
+        <v>49.3798768</v>
       </c>
       <c r="D301" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B302" t="n">
         <v>0</v>
       </c>
       <c r="C302" t="n">
-        <v>31.96714579</v>
+        <v>64.29568789</v>
       </c>
       <c r="D302" t="b">
         <v>1</v>
@@ -4669,27 +4669,27 @@
         <v>0</v>
       </c>
       <c r="B303" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C303" t="n">
-        <v>132.8952772</v>
+        <v>8.082135524</v>
       </c>
       <c r="D303" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B304" t="n">
         <v>0</v>
       </c>
       <c r="C304" t="n">
-        <v>32.32854209</v>
+        <v>61.73305955</v>
       </c>
       <c r="D304" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="305">
@@ -4700,35 +4700,35 @@
         <v>1</v>
       </c>
       <c r="C305" t="n">
-        <v>26.4476386</v>
+        <v>66.69404517</v>
       </c>
       <c r="D305" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B306" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C306" t="n">
-        <v>51.94250513</v>
+        <v>24.21355236</v>
       </c>
       <c r="D306" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B307" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C307" t="n">
-        <v>44.97741273</v>
+        <v>17.83983573</v>
       </c>
       <c r="D307" t="b">
         <v>1</v>
@@ -4742,21 +4742,21 @@
         <v>1</v>
       </c>
       <c r="C308" t="n">
-        <v>19.71252567</v>
+        <v>9.034907598</v>
       </c>
       <c r="D308" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B309" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C309" t="n">
-        <v>4.073921971</v>
+        <v>49.31416838</v>
       </c>
       <c r="D309" t="b">
         <v>1</v>
@@ -4764,16 +4764,16 @@
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B310" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C310" t="n">
-        <v>7.162217659</v>
+        <v>11.99178645</v>
       </c>
       <c r="D310" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="311">
@@ -4781,13 +4781,13 @@
         <v>0</v>
       </c>
       <c r="B311" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C311" t="n">
-        <v>26.21765914</v>
+        <v>66.69404517</v>
       </c>
       <c r="D311" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="312">
@@ -4795,10 +4795,10 @@
         <v>0</v>
       </c>
       <c r="B312" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C312" t="n">
-        <v>11.49897331</v>
+        <v>4.533880903</v>
       </c>
       <c r="D312" t="b">
         <v>1</v>
@@ -4809,10 +4809,10 @@
         <v>0</v>
       </c>
       <c r="B313" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C313" t="n">
-        <v>17.41273101</v>
+        <v>3.252566735</v>
       </c>
       <c r="D313" t="b">
         <v>1</v>
@@ -4826,7 +4826,7 @@
         <v>1</v>
       </c>
       <c r="C314" t="n">
-        <v>16.85420945</v>
+        <v>34.59548255</v>
       </c>
       <c r="D314" t="b">
         <v>0</v>
@@ -4834,13 +4834,13 @@
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B315" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C315" t="n">
-        <v>43.92607803</v>
+        <v>33.3798768</v>
       </c>
       <c r="D315" t="b">
         <v>1</v>
@@ -4848,16 +4848,16 @@
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B316" t="n">
         <v>0</v>
       </c>
       <c r="C316" t="n">
-        <v>14.6201232</v>
+        <v>3.58110883</v>
       </c>
       <c r="D316" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="317">
@@ -4865,27 +4865,27 @@
         <v>0</v>
       </c>
       <c r="B317" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C317" t="n">
-        <v>27.23613963</v>
+        <v>71.2936345</v>
       </c>
       <c r="D317" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C318" t="n">
-        <v>6.176591376</v>
+        <v>43.95893224</v>
       </c>
       <c r="D318" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319">
@@ -4893,13 +4893,13 @@
         <v>0</v>
       </c>
       <c r="B319" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C319" t="n">
-        <v>11.72895277</v>
+        <v>37.09240246</v>
       </c>
       <c r="D319" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="320">
@@ -4907,10 +4907,10 @@
         <v>0</v>
       </c>
       <c r="B320" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C320" t="n">
-        <v>92.64887064</v>
+        <v>34.59548255</v>
       </c>
       <c r="D320" t="b">
         <v>0</v>
@@ -4921,10 +4921,10 @@
         <v>0</v>
       </c>
       <c r="B321" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C321" t="n">
-        <v>132.8952772</v>
+        <v>9.691991786000001</v>
       </c>
       <c r="D321" t="b">
         <v>0</v>
@@ -4938,10 +4938,10 @@
         <v>1</v>
       </c>
       <c r="C322" t="n">
-        <v>74.05338809</v>
+        <v>8.837782341</v>
       </c>
       <c r="D322" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="323">
@@ -4952,10 +4952,10 @@
         <v>1</v>
       </c>
       <c r="C323" t="n">
-        <v>60.25462012</v>
+        <v>50.20123203</v>
       </c>
       <c r="D323" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="324">
@@ -4966,21 +4966,21 @@
         <v>1</v>
       </c>
       <c r="C324" t="n">
-        <v>34.59548255</v>
+        <v>6.603696099</v>
       </c>
       <c r="D324" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B325" t="n">
         <v>0</v>
       </c>
       <c r="C325" t="n">
-        <v>7.030800821</v>
+        <v>9.790554415000001</v>
       </c>
       <c r="D325" t="b">
         <v>1</v>
@@ -4994,7 +4994,7 @@
         <v>0</v>
       </c>
       <c r="C326" t="n">
-        <v>80.98562628000001</v>
+        <v>2.201232033</v>
       </c>
       <c r="D326" t="b">
         <v>1</v>
@@ -5008,7 +5008,7 @@
         <v>1</v>
       </c>
       <c r="C327" t="n">
-        <v>19.58110883</v>
+        <v>63.11293634</v>
       </c>
       <c r="D327" t="b">
         <v>1</v>
@@ -5016,13 +5016,13 @@
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B328" t="n">
         <v>0</v>
       </c>
       <c r="C328" t="n">
-        <v>7.589322382</v>
+        <v>22.37371663</v>
       </c>
       <c r="D328" t="b">
         <v>1</v>
@@ -5030,16 +5030,16 @@
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B329" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C329" t="n">
-        <v>93.8973306</v>
+        <v>25.65913758</v>
       </c>
       <c r="D329" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330">
@@ -5050,10 +5050,10 @@
         <v>0</v>
       </c>
       <c r="C330" t="n">
-        <v>17.01848049</v>
+        <v>20.30390144</v>
       </c>
       <c r="D330" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="331">
@@ -5064,10 +5064,10 @@
         <v>1</v>
       </c>
       <c r="C331" t="n">
-        <v>15.34291581</v>
+        <v>7.195071869</v>
       </c>
       <c r="D331" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="332">
@@ -5075,10 +5075,10 @@
         <v>0</v>
       </c>
       <c r="B332" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C332" t="n">
-        <v>35.74537988</v>
+        <v>11.8275154</v>
       </c>
       <c r="D332" t="b">
         <v>1</v>
@@ -5092,7 +5092,7 @@
         <v>1</v>
       </c>
       <c r="C333" t="n">
-        <v>3.975359343</v>
+        <v>7.589322382</v>
       </c>
       <c r="D333" t="b">
         <v>1</v>
@@ -5103,10 +5103,10 @@
         <v>0</v>
       </c>
       <c r="B334" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C334" t="n">
-        <v>26.21765914</v>
+        <v>123.3347023</v>
       </c>
       <c r="D334" t="b">
         <v>1</v>
@@ -5117,13 +5117,13 @@
         <v>0</v>
       </c>
       <c r="B335" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C335" t="n">
-        <v>57.62628337</v>
+        <v>14.58726899</v>
       </c>
       <c r="D335" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="336">
@@ -5134,21 +5134,21 @@
         <v>1</v>
       </c>
       <c r="C336" t="n">
-        <v>129.2813142</v>
+        <v>163.8110883</v>
       </c>
       <c r="D336" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B337" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C337" t="n">
-        <v>4.993839836</v>
+        <v>21.65092402</v>
       </c>
       <c r="D337" t="b">
         <v>0</v>
@@ -5156,27 +5156,27 @@
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B338" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C338" t="n">
-        <v>24.27926078</v>
+        <v>15.73716632</v>
       </c>
       <c r="D338" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B339" t="n">
         <v>1</v>
       </c>
       <c r="C339" t="n">
-        <v>67.84394251000001</v>
+        <v>17.60985626</v>
       </c>
       <c r="D339" t="b">
         <v>1</v>
@@ -5187,13 +5187,13 @@
         <v>0</v>
       </c>
       <c r="B340" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C340" t="n">
-        <v>58.21765914</v>
+        <v>59.20328542</v>
       </c>
       <c r="D340" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="341">
@@ -5201,27 +5201,27 @@
         <v>0</v>
       </c>
       <c r="B341" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C341" t="n">
-        <v>49.70841889</v>
+        <v>14.85010267</v>
       </c>
       <c r="D341" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B342" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C342" t="n">
-        <v>8.410677617999999</v>
+        <v>12.12320329</v>
       </c>
       <c r="D342" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="343">
@@ -5232,10 +5232,10 @@
         <v>1</v>
       </c>
       <c r="C343" t="n">
-        <v>20.56673511</v>
+        <v>42.18480493</v>
       </c>
       <c r="D343" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="344">
@@ -5243,24 +5243,24 @@
         <v>0</v>
       </c>
       <c r="B344" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C344" t="n">
-        <v>24.3449692</v>
+        <v>9.691991786000001</v>
       </c>
       <c r="D344" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B345" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C345" t="n">
-        <v>21.15811088</v>
+        <v>164.5667351</v>
       </c>
       <c r="D345" t="b">
         <v>0</v>
@@ -5274,7 +5274,7 @@
         <v>1</v>
       </c>
       <c r="C346" t="n">
-        <v>23.45790554</v>
+        <v>5.125256674</v>
       </c>
       <c r="D346" t="b">
         <v>0</v>
@@ -5288,7 +5288,7 @@
         <v>1</v>
       </c>
       <c r="C347" t="n">
-        <v>35.84394251</v>
+        <v>52.10677618</v>
       </c>
       <c r="D347" t="b">
         <v>0</v>
@@ -5296,13 +5296,13 @@
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B348" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C348" t="n">
-        <v>16.49281314</v>
+        <v>27.40041068</v>
       </c>
       <c r="D348" t="b">
         <v>0</v>
@@ -5316,10 +5316,10 @@
         <v>1</v>
       </c>
       <c r="C349" t="n">
-        <v>34.03696099</v>
+        <v>32.45995893</v>
       </c>
       <c r="D349" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="350">
@@ -5327,10 +5327,10 @@
         <v>0</v>
       </c>
       <c r="B350" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C350" t="n">
-        <v>34.49691992</v>
+        <v>59.99178645</v>
       </c>
       <c r="D350" t="b">
         <v>0</v>
@@ -5344,7 +5344,7 @@
         <v>0</v>
       </c>
       <c r="C351" t="n">
-        <v>22.73511294</v>
+        <v>90.51334702</v>
       </c>
       <c r="D351" t="b">
         <v>1</v>
@@ -5352,16 +5352,16 @@
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B352" t="n">
         <v>0</v>
       </c>
       <c r="C352" t="n">
-        <v>81.64271047</v>
+        <v>9.790554415000001</v>
       </c>
       <c r="D352" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353">
@@ -5372,10 +5372,10 @@
         <v>1</v>
       </c>
       <c r="C353" t="n">
-        <v>128.1314168</v>
+        <v>23.95071869</v>
       </c>
       <c r="D353" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="354">
@@ -5386,10 +5386,10 @@
         <v>0</v>
       </c>
       <c r="C354" t="n">
-        <v>7.162217659</v>
+        <v>8.016427105</v>
       </c>
       <c r="D354" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="355">
@@ -5400,21 +5400,21 @@
         <v>1</v>
       </c>
       <c r="C355" t="n">
-        <v>115.5482546</v>
+        <v>12.8788501</v>
       </c>
       <c r="D355" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B356" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C356" t="n">
-        <v>17.60985626</v>
+        <v>14.71868583</v>
       </c>
       <c r="D356" t="b">
         <v>1</v>
@@ -5425,13 +5425,13 @@
         <v>0</v>
       </c>
       <c r="B357" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C357" t="n">
-        <v>6.800821355</v>
+        <v>23.2936345</v>
       </c>
       <c r="D357" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="358">
@@ -5442,10 +5442,10 @@
         <v>1</v>
       </c>
       <c r="C358" t="n">
-        <v>42.18480493</v>
+        <v>49.87268994</v>
       </c>
       <c r="D358" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="359">
@@ -5456,7 +5456,7 @@
         <v>1</v>
       </c>
       <c r="C359" t="n">
-        <v>28.15605749</v>
+        <v>15.57289528</v>
       </c>
       <c r="D359" t="b">
         <v>1</v>
@@ -5464,16 +5464,16 @@
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B360" t="n">
         <v>0</v>
       </c>
       <c r="C360" t="n">
-        <v>51.58110883</v>
+        <v>45.96303901</v>
       </c>
       <c r="D360" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="361">
@@ -5484,10 +5484,10 @@
         <v>0</v>
       </c>
       <c r="C361" t="n">
-        <v>3.811088296</v>
+        <v>56.77207392</v>
       </c>
       <c r="D361" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="362">
@@ -5498,7 +5498,7 @@
         <v>1</v>
       </c>
       <c r="C362" t="n">
-        <v>5.848049281</v>
+        <v>68.27104722999999</v>
       </c>
       <c r="D362" t="b">
         <v>1</v>
@@ -5506,16 +5506,16 @@
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B363" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C363" t="n">
-        <v>15.60574949</v>
+        <v>13.10882957</v>
       </c>
       <c r="D363" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="364">
@@ -5523,13 +5523,13 @@
         <v>0</v>
       </c>
       <c r="B364" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C364" t="n">
-        <v>19.05544148</v>
+        <v>5.32238193</v>
       </c>
       <c r="D364" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365">
@@ -5537,10 +5537,10 @@
         <v>0</v>
       </c>
       <c r="B365" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C365" t="n">
-        <v>73.13347023</v>
+        <v>16.78850103</v>
       </c>
       <c r="D365" t="b">
         <v>0</v>
@@ -5551,13 +5551,13 @@
         <v>0</v>
       </c>
       <c r="B366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C366" t="n">
-        <v>89.00205339</v>
+        <v>13.9301848</v>
       </c>
       <c r="D366" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="367">
@@ -5565,10 +5565,10 @@
         <v>0</v>
       </c>
       <c r="B367" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C367" t="n">
-        <v>79.80287473999999</v>
+        <v>163.7782341</v>
       </c>
       <c r="D367" t="b">
         <v>0</v>
@@ -5582,7 +5582,7 @@
         <v>1</v>
       </c>
       <c r="C368" t="n">
-        <v>10.51334702</v>
+        <v>23.45790554</v>
       </c>
       <c r="D368" t="b">
         <v>0</v>
@@ -5590,13 +5590,13 @@
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B369" t="n">
         <v>0</v>
       </c>
       <c r="C369" t="n">
-        <v>9.034907598</v>
+        <v>5.158110883</v>
       </c>
       <c r="D369" t="b">
         <v>0</v>
@@ -5610,10 +5610,10 @@
         <v>1</v>
       </c>
       <c r="C370" t="n">
-        <v>63.54004107</v>
+        <v>7.819301848</v>
       </c>
       <c r="D370" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="371">
@@ -5624,7 +5624,7 @@
         <v>1</v>
       </c>
       <c r="C371" t="n">
-        <v>10.84188912</v>
+        <v>21.35523614</v>
       </c>
       <c r="D371" t="b">
         <v>1</v>
@@ -5632,27 +5632,27 @@
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B372" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C372" t="n">
-        <v>27.4661191</v>
+        <v>42.48049281</v>
       </c>
       <c r="D372" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B373" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C373" t="n">
-        <v>8.87063655</v>
+        <v>18.16837782</v>
       </c>
       <c r="D373" t="b">
         <v>1</v>
@@ -5660,13 +5660,13 @@
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C374" t="n">
-        <v>128.0657084</v>
+        <v>15.01437372</v>
       </c>
       <c r="D374" t="b">
         <v>0</v>
@@ -5677,27 +5677,27 @@
         <v>0</v>
       </c>
       <c r="B375" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C375" t="n">
-        <v>32.88706366</v>
+        <v>28.58316222</v>
       </c>
       <c r="D375" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B376" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C376" t="n">
-        <v>15.93429158</v>
+        <v>63.14579055</v>
       </c>
       <c r="D376" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="377">
@@ -5708,35 +5708,35 @@
         <v>1</v>
       </c>
       <c r="C377" t="n">
-        <v>60.78028747</v>
+        <v>44.78028747</v>
       </c>
       <c r="D377" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B378" t="n">
         <v>0</v>
       </c>
       <c r="C378" t="n">
-        <v>5.650924025</v>
+        <v>85.48665298</v>
       </c>
       <c r="D378" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B379" t="n">
         <v>0</v>
       </c>
       <c r="C379" t="n">
-        <v>9.790554415000001</v>
+        <v>3.58110883</v>
       </c>
       <c r="D379" t="b">
         <v>1</v>
@@ -5744,13 +5744,13 @@
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B380" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C380" t="n">
-        <v>18.7926078</v>
+        <v>21.88090349</v>
       </c>
       <c r="D380" t="b">
         <v>0</v>
@@ -5764,24 +5764,24 @@
         <v>1</v>
       </c>
       <c r="C381" t="n">
-        <v>36.73100616</v>
+        <v>12.09034908</v>
       </c>
       <c r="D381" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B382" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C382" t="n">
-        <v>13.17453799</v>
+        <v>11.76180698</v>
       </c>
       <c r="D382" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="383">
@@ -5789,10 +5789,10 @@
         <v>0</v>
       </c>
       <c r="B383" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C383" t="n">
-        <v>94.12731006</v>
+        <v>10.38193018</v>
       </c>
       <c r="D383" t="b">
         <v>0</v>
@@ -5800,13 +5800,13 @@
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B384" t="n">
         <v>0</v>
       </c>
       <c r="C384" t="n">
-        <v>27.56468172</v>
+        <v>8.213552361</v>
       </c>
       <c r="D384" t="b">
         <v>0</v>
@@ -5814,13 +5814,13 @@
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B385" t="n">
         <v>1</v>
       </c>
       <c r="C385" t="n">
-        <v>53.19096509</v>
+        <v>17.57700205</v>
       </c>
       <c r="D385" t="b">
         <v>1</v>
@@ -5834,7 +5834,7 @@
         <v>1</v>
       </c>
       <c r="C386" t="n">
-        <v>1.80698152</v>
+        <v>23.45790554</v>
       </c>
       <c r="D386" t="b">
         <v>0</v>
@@ -5842,16 +5842,16 @@
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B387" t="n">
         <v>0</v>
       </c>
       <c r="C387" t="n">
-        <v>18.56262834</v>
+        <v>4.435318275</v>
       </c>
       <c r="D387" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="388">
@@ -5859,24 +5859,24 @@
         <v>1</v>
       </c>
       <c r="B388" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C388" t="n">
-        <v>3.416837782</v>
+        <v>38.53798768</v>
       </c>
       <c r="D388" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B389" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C389" t="n">
-        <v>26.94045175</v>
+        <v>40.87063655</v>
       </c>
       <c r="D389" t="b">
         <v>1</v>
@@ -5890,7 +5890,7 @@
         <v>1</v>
       </c>
       <c r="C390" t="n">
-        <v>45.07597536</v>
+        <v>4.928131417</v>
       </c>
       <c r="D390" t="b">
         <v>0</v>
@@ -5898,16 +5898,16 @@
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B391" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C391" t="n">
-        <v>49.7412731</v>
+        <v>20.92813142</v>
       </c>
       <c r="D391" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="392">
@@ -5918,7 +5918,7 @@
         <v>1</v>
       </c>
       <c r="C392" t="n">
-        <v>4.960985626</v>
+        <v>9.100616016</v>
       </c>
       <c r="D392" t="b">
         <v>1</v>
@@ -5926,13 +5926,13 @@
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B393" t="n">
         <v>1</v>
       </c>
       <c r="C393" t="n">
-        <v>41.69199179</v>
+        <v>39.22792608</v>
       </c>
       <c r="D393" t="b">
         <v>1</v>
@@ -5946,10 +5946,10 @@
         <v>0</v>
       </c>
       <c r="C394" t="n">
-        <v>54.07802875</v>
+        <v>4.1724846</v>
       </c>
       <c r="D394" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="395">
@@ -5957,13 +5957,13 @@
         <v>0</v>
       </c>
       <c r="B395" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C395" t="n">
-        <v>0.492813142</v>
+        <v>36.23819302</v>
       </c>
       <c r="D395" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="396">
@@ -5971,27 +5971,27 @@
         <v>0</v>
       </c>
       <c r="B396" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C396" t="n">
-        <v>26.67761807</v>
+        <v>16.22997947</v>
       </c>
       <c r="D396" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B397" t="n">
         <v>0</v>
       </c>
       <c r="C397" t="n">
-        <v>25.98767967</v>
+        <v>11.76180698</v>
       </c>
       <c r="D397" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="398">
@@ -6002,7 +6002,7 @@
         <v>1</v>
       </c>
       <c r="C398" t="n">
-        <v>3.121149897</v>
+        <v>8.739219713000001</v>
       </c>
       <c r="D398" t="b">
         <v>0</v>
@@ -6016,7 +6016,7 @@
         <v>0</v>
       </c>
       <c r="C399" t="n">
-        <v>6.078028747</v>
+        <v>72.57494867</v>
       </c>
       <c r="D399" t="b">
         <v>0</v>
@@ -6027,10 +6027,10 @@
         <v>0</v>
       </c>
       <c r="B400" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C400" t="n">
-        <v>11.79466119</v>
+        <v>67.4825462</v>
       </c>
       <c r="D400" t="b">
         <v>0</v>
@@ -6038,13 +6038,13 @@
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B401" t="n">
         <v>0</v>
       </c>
       <c r="C401" t="n">
-        <v>7.852156057</v>
+        <v>41.65913758</v>
       </c>
       <c r="D401" t="b">
         <v>0</v>
@@ -6058,10 +6058,10 @@
         <v>1</v>
       </c>
       <c r="C402" t="n">
-        <v>8.607802875000001</v>
+        <v>1.971252567</v>
       </c>
       <c r="D402" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="403">
@@ -6072,7 +6072,7 @@
         <v>1</v>
       </c>
       <c r="C403" t="n">
-        <v>12.78028747</v>
+        <v>118.899384</v>
       </c>
       <c r="D403" t="b">
         <v>1</v>
@@ -6086,7 +6086,7 @@
         <v>0</v>
       </c>
       <c r="C404" t="n">
-        <v>22.73511294</v>
+        <v>59.00616016</v>
       </c>
       <c r="D404" t="b">
         <v>1</v>
@@ -6094,13 +6094,13 @@
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B405" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C405" t="n">
-        <v>1.347022587</v>
+        <v>11.26899384</v>
       </c>
       <c r="D405" t="b">
         <v>0</v>
@@ -6114,7 +6114,7 @@
         <v>1</v>
       </c>
       <c r="C406" t="n">
-        <v>2.39835729</v>
+        <v>36.59958932</v>
       </c>
       <c r="D406" t="b">
         <v>0</v>
@@ -6122,16 +6122,16 @@
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B407" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C407" t="n">
-        <v>15.14579055</v>
+        <v>15.86858316</v>
       </c>
       <c r="D407" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="408">
@@ -6139,13 +6139,13 @@
         <v>0</v>
       </c>
       <c r="B408" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C408" t="n">
-        <v>23.9835729</v>
+        <v>45.73305955</v>
       </c>
       <c r="D408" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="409">
@@ -6156,7 +6156,7 @@
         <v>1</v>
       </c>
       <c r="C409" t="n">
-        <v>23.95071869</v>
+        <v>16.39425051</v>
       </c>
       <c r="D409" t="b">
         <v>1</v>
@@ -6170,7 +6170,7 @@
         <v>1</v>
       </c>
       <c r="C410" t="n">
-        <v>13.73305955</v>
+        <v>155.3675565</v>
       </c>
       <c r="D410" t="b">
         <v>0</v>
@@ -6178,13 +6178,13 @@
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B411" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C411" t="n">
-        <v>33.57700205</v>
+        <v>58.94045175</v>
       </c>
       <c r="D411" t="b">
         <v>0</v>
@@ -6198,10 +6198,10 @@
         <v>1</v>
       </c>
       <c r="C412" t="n">
-        <v>34.56262834</v>
+        <v>1.445585216</v>
       </c>
       <c r="D412" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="413">
@@ -6212,10 +6212,10 @@
         <v>1</v>
       </c>
       <c r="C413" t="n">
-        <v>7.12936345</v>
+        <v>13.5687885</v>
       </c>
       <c r="D413" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414">
@@ -6226,21 +6226,21 @@
         <v>1</v>
       </c>
       <c r="C414" t="n">
-        <v>70.93223819000001</v>
+        <v>39.06365503</v>
       </c>
       <c r="D414" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B415" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C415" t="n">
-        <v>123.0718686</v>
+        <v>17.93839836</v>
       </c>
       <c r="D415" t="b">
         <v>1</v>
@@ -6254,7 +6254,7 @@
         <v>1</v>
       </c>
       <c r="C416" t="n">
-        <v>48.09856263</v>
+        <v>16.78850103</v>
       </c>
       <c r="D416" t="b">
         <v>1</v>
@@ -6262,13 +6262,13 @@
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B417" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C417" t="n">
-        <v>44.48459959</v>
+        <v>15.11293634</v>
       </c>
       <c r="D417" t="b">
         <v>0</v>
@@ -6279,13 +6279,13 @@
         <v>0</v>
       </c>
       <c r="B418" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C418" t="n">
-        <v>36.59958932</v>
+        <v>22.47227926</v>
       </c>
       <c r="D418" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="419">
@@ -6296,7 +6296,7 @@
         <v>0</v>
       </c>
       <c r="C419" t="n">
-        <v>12.05749487</v>
+        <v>155.1704312</v>
       </c>
       <c r="D419" t="b">
         <v>1</v>
@@ -6304,16 +6304,16 @@
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B420" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C420" t="n">
-        <v>103.5893224</v>
+        <v>24.08213552</v>
       </c>
       <c r="D420" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421">
@@ -6321,10 +6321,10 @@
         <v>0</v>
       </c>
       <c r="B421" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C421" t="n">
-        <v>82.7926078</v>
+        <v>17.24845996</v>
       </c>
       <c r="D421" t="b">
         <v>0</v>
@@ -6338,21 +6338,21 @@
         <v>1</v>
       </c>
       <c r="C422" t="n">
-        <v>101.5195072</v>
+        <v>8.640657084000001</v>
       </c>
       <c r="D422" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B423" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C423" t="n">
-        <v>11.56468172</v>
+        <v>60.78028747</v>
       </c>
       <c r="D423" t="b">
         <v>0</v>
@@ -6360,13 +6360,13 @@
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B424" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C424" t="n">
-        <v>7.950718686</v>
+        <v>105.9219713</v>
       </c>
       <c r="D424" t="b">
         <v>0</v>
@@ -6380,7 +6380,7 @@
         <v>1</v>
       </c>
       <c r="C425" t="n">
-        <v>46.9486653</v>
+        <v>2.168377823</v>
       </c>
       <c r="D425" t="b">
         <v>0</v>
@@ -6391,10 +6391,10 @@
         <v>0</v>
       </c>
       <c r="B426" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C426" t="n">
-        <v>65.37987680000001</v>
+        <v>52.00821355</v>
       </c>
       <c r="D426" t="b">
         <v>0</v>
@@ -6408,7 +6408,7 @@
         <v>1</v>
       </c>
       <c r="C427" t="n">
-        <v>44.02464066</v>
+        <v>11.69609856</v>
       </c>
       <c r="D427" t="b">
         <v>1</v>
@@ -6416,16 +6416,16 @@
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B428" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C428" t="n">
-        <v>12.25462012</v>
+        <v>23.19507187</v>
       </c>
       <c r="D428" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="429">
@@ -6436,7 +6436,7 @@
         <v>1</v>
       </c>
       <c r="C429" t="n">
-        <v>39.68788501</v>
+        <v>19.31827515</v>
       </c>
       <c r="D429" t="b">
         <v>0</v>
@@ -6444,16 +6444,16 @@
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B430" t="n">
         <v>1</v>
       </c>
       <c r="C430" t="n">
-        <v>50.23408624</v>
+        <v>26.18480493</v>
       </c>
       <c r="D430" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="431">
@@ -6461,13 +6461,13 @@
         <v>0</v>
       </c>
       <c r="B431" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C431" t="n">
-        <v>13.40451745</v>
+        <v>70.34086241999999</v>
       </c>
       <c r="D431" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="432">
@@ -6478,7 +6478,7 @@
         <v>0</v>
       </c>
       <c r="C432" t="n">
-        <v>13.40451745</v>
+        <v>18.95687885</v>
       </c>
       <c r="D432" t="b">
         <v>1</v>
@@ -6486,44 +6486,44 @@
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B433" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C433" t="n">
-        <v>9.067761807</v>
+        <v>23.95071869</v>
       </c>
       <c r="D433" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B434" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C434" t="n">
-        <v>40.31211499</v>
+        <v>32.49281314</v>
       </c>
       <c r="D434" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B435" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C435" t="n">
-        <v>16.06570842</v>
+        <v>5.815195072</v>
       </c>
       <c r="D435" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="436">
@@ -6534,10 +6534,10 @@
         <v>1</v>
       </c>
       <c r="C436" t="n">
-        <v>38.86652977</v>
+        <v>2.431211499</v>
       </c>
       <c r="D436" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="437">
@@ -6548,21 +6548,21 @@
         <v>1</v>
       </c>
       <c r="C437" t="n">
-        <v>22.63655031</v>
+        <v>33.90554415</v>
       </c>
       <c r="D437" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B438" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C438" t="n">
-        <v>9.199178645</v>
+        <v>19.84394251</v>
       </c>
       <c r="D438" t="b">
         <v>1</v>
@@ -6576,35 +6576,35 @@
         <v>1</v>
       </c>
       <c r="C439" t="n">
-        <v>40.37782341</v>
+        <v>6.669404517</v>
       </c>
       <c r="D439" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B440" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C440" t="n">
-        <v>42.38193018</v>
+        <v>22.24229979</v>
       </c>
       <c r="D440" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B441" t="n">
         <v>0</v>
       </c>
       <c r="C441" t="n">
-        <v>61.73305955</v>
+        <v>49.31416838</v>
       </c>
       <c r="D441" t="b">
         <v>1</v>
@@ -6612,16 +6612,16 @@
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B442" t="n">
         <v>0</v>
       </c>
       <c r="C442" t="n">
-        <v>46.35728953</v>
+        <v>5.848049281</v>
       </c>
       <c r="D442" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="443">
@@ -6629,10 +6629,10 @@
         <v>0</v>
       </c>
       <c r="B443" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C443" t="n">
-        <v>3.975359343</v>
+        <v>14.98151951</v>
       </c>
       <c r="D443" t="b">
         <v>1</v>
@@ -6640,27 +6640,27 @@
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B444" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C444" t="n">
-        <v>51.31827515</v>
+        <v>16.42710472</v>
       </c>
       <c r="D444" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B445" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C445" t="n">
-        <v>27.92607803</v>
+        <v>6.045174538</v>
       </c>
       <c r="D445" t="b">
         <v>0</v>
@@ -6671,27 +6671,27 @@
         <v>0</v>
       </c>
       <c r="B446" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C446" t="n">
-        <v>78.68583162</v>
+        <v>37.38809035</v>
       </c>
       <c r="D446" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B447" t="n">
         <v>0</v>
       </c>
       <c r="C447" t="n">
-        <v>61.07597536</v>
+        <v>52.73100616</v>
       </c>
       <c r="D447" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="448">
@@ -6699,10 +6699,10 @@
         <v>0</v>
       </c>
       <c r="B448" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C448" t="n">
-        <v>79.54004107</v>
+        <v>86.66940452</v>
       </c>
       <c r="D448" t="b">
         <v>0</v>
@@ -6716,7 +6716,7 @@
         <v>1</v>
       </c>
       <c r="C449" t="n">
-        <v>166.275154</v>
+        <v>27.36755647</v>
       </c>
       <c r="D449" t="b">
         <v>1</v>
@@ -6724,16 +6724,16 @@
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B450" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C450" t="n">
-        <v>3.811088296</v>
+        <v>7.523613963</v>
       </c>
       <c r="D450" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="451">
@@ -6744,10 +6744,10 @@
         <v>1</v>
       </c>
       <c r="C451" t="n">
-        <v>34.56262834</v>
+        <v>54.9650924</v>
       </c>
       <c r="D451" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="452">
@@ -6755,13 +6755,13 @@
         <v>0</v>
       </c>
       <c r="B452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C452" t="n">
-        <v>9.429158111</v>
+        <v>50.98973306</v>
       </c>
       <c r="D452" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="453">
@@ -6772,10 +6772,10 @@
         <v>1</v>
       </c>
       <c r="C453" t="n">
-        <v>68.27104722999999</v>
+        <v>33.41273101</v>
       </c>
       <c r="D453" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="454">
@@ -6783,10 +6783,10 @@
         <v>0</v>
       </c>
       <c r="B454" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C454" t="n">
-        <v>5.9137577</v>
+        <v>5.585215606</v>
       </c>
       <c r="D454" t="b">
         <v>0</v>
@@ -6794,27 +6794,27 @@
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B455" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C455" t="n">
-        <v>5.420944559</v>
+        <v>99.77823409</v>
       </c>
       <c r="D455" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B456" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C456" t="n">
-        <v>6.53798768</v>
+        <v>32.85420945</v>
       </c>
       <c r="D456" t="b">
         <v>1</v>
@@ -6825,10 +6825,10 @@
         <v>0</v>
       </c>
       <c r="B457" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C457" t="n">
-        <v>3.975359343</v>
+        <v>70.93223819000001</v>
       </c>
       <c r="D457" t="b">
         <v>1</v>
@@ -6839,10 +6839,10 @@
         <v>0</v>
       </c>
       <c r="B458" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C458" t="n">
-        <v>73.49486653</v>
+        <v>11.49897331</v>
       </c>
       <c r="D458" t="b">
         <v>1</v>
@@ -6856,7 +6856,7 @@
         <v>1</v>
       </c>
       <c r="C459" t="n">
-        <v>6.275154004</v>
+        <v>70.83367556</v>
       </c>
       <c r="D459" t="b">
         <v>1</v>
@@ -6867,10 +6867,10 @@
         <v>0</v>
       </c>
       <c r="B460" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C460" t="n">
-        <v>35.84394251</v>
+        <v>86.04517454</v>
       </c>
       <c r="D460" t="b">
         <v>0</v>
@@ -6881,13 +6881,13 @@
         <v>0</v>
       </c>
       <c r="B461" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C461" t="n">
-        <v>0.689938398</v>
+        <v>35.28542094</v>
       </c>
       <c r="D461" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="462">
@@ -6895,13 +6895,13 @@
         <v>0</v>
       </c>
       <c r="B462" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C462" t="n">
-        <v>49.14989733</v>
+        <v>84.04106776</v>
       </c>
       <c r="D462" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="463">
@@ -6912,7 +6912,7 @@
         <v>1</v>
       </c>
       <c r="C463" t="n">
-        <v>36.59958932</v>
+        <v>20.89527721</v>
       </c>
       <c r="D463" t="b">
         <v>0</v>
@@ -6926,10 +6926,10 @@
         <v>0</v>
       </c>
       <c r="C464" t="n">
-        <v>30.12731006</v>
+        <v>45.30595483</v>
       </c>
       <c r="D464" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="465">
@@ -6940,7 +6940,7 @@
         <v>0</v>
       </c>
       <c r="C465" t="n">
-        <v>72.67351128999999</v>
+        <v>15.70431211</v>
       </c>
       <c r="D465" t="b">
         <v>0</v>
@@ -6954,7 +6954,7 @@
         <v>1</v>
       </c>
       <c r="C466" t="n">
-        <v>8.180698152</v>
+        <v>5.519507187</v>
       </c>
       <c r="D466" t="b">
         <v>0</v>
@@ -6962,13 +6962,13 @@
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B467" t="n">
         <v>1</v>
       </c>
       <c r="C467" t="n">
-        <v>6.439425051</v>
+        <v>23.6550308</v>
       </c>
       <c r="D467" t="b">
         <v>1</v>
@@ -6979,10 +6979,10 @@
         <v>0</v>
       </c>
       <c r="B468" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C468" t="n">
-        <v>95.21149896999999</v>
+        <v>3.482546201</v>
       </c>
       <c r="D468" t="b">
         <v>1</v>
@@ -6996,7 +6996,7 @@
         <v>1</v>
       </c>
       <c r="C469" t="n">
-        <v>38.76796715</v>
+        <v>40.3449692</v>
       </c>
       <c r="D469" t="b">
         <v>1</v>
@@ -7004,16 +7004,16 @@
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B470" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C470" t="n">
-        <v>110.4887064</v>
+        <v>2.759753593</v>
       </c>
       <c r="D470" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="471">
@@ -7024,21 +7024,21 @@
         <v>0</v>
       </c>
       <c r="C471" t="n">
-        <v>0.492813142</v>
+        <v>45.30595483</v>
       </c>
       <c r="D471" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B472" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C472" t="n">
-        <v>29.24024641</v>
+        <v>9.100616016</v>
       </c>
       <c r="D472" t="b">
         <v>1</v>
@@ -7052,7 +7052,7 @@
         <v>1</v>
       </c>
       <c r="C473" t="n">
-        <v>20.96098563</v>
+        <v>11.23613963</v>
       </c>
       <c r="D473" t="b">
         <v>1</v>
@@ -7063,13 +7063,13 @@
         <v>0</v>
       </c>
       <c r="B474" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C474" t="n">
-        <v>1.708418891</v>
+        <v>5.848049281</v>
       </c>
       <c r="D474" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="475">
@@ -7077,10 +7077,10 @@
         <v>0</v>
       </c>
       <c r="B475" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C475" t="n">
-        <v>58.80903491</v>
+        <v>18.49691992</v>
       </c>
       <c r="D475" t="b">
         <v>1</v>
@@ -7091,13 +7091,13 @@
         <v>0</v>
       </c>
       <c r="B476" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C476" t="n">
-        <v>11.72895277</v>
+        <v>8.410677617999999</v>
       </c>
       <c r="D476" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="477">
@@ -7108,7 +7108,7 @@
         <v>1</v>
       </c>
       <c r="C477" t="n">
-        <v>30.22587269</v>
+        <v>49.47843943</v>
       </c>
       <c r="D477" t="b">
         <v>0</v>
@@ -7116,13 +7116,13 @@
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B478" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C478" t="n">
-        <v>179.449692</v>
+        <v>49.41273101</v>
       </c>
       <c r="D478" t="b">
         <v>0</v>
@@ -7136,10 +7136,10 @@
         <v>1</v>
       </c>
       <c r="C479" t="n">
-        <v>22.9650924</v>
+        <v>105.8234086</v>
       </c>
       <c r="D479" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="480">
@@ -7147,10 +7147,10 @@
         <v>0</v>
       </c>
       <c r="B480" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C480" t="n">
-        <v>23.55646817</v>
+        <v>59.99178645</v>
       </c>
       <c r="D480" t="b">
         <v>0</v>
@@ -7164,7 +7164,7 @@
         <v>1</v>
       </c>
       <c r="C481" t="n">
-        <v>14.55441478</v>
+        <v>58.94045175</v>
       </c>
       <c r="D481" t="b">
         <v>0</v>
@@ -7178,21 +7178,21 @@
         <v>0</v>
       </c>
       <c r="C482" t="n">
-        <v>59.20328542</v>
+        <v>17.11704312</v>
       </c>
       <c r="D482" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B483" t="n">
         <v>1</v>
       </c>
       <c r="C483" t="n">
-        <v>5.94661191</v>
+        <v>81.24845996000001</v>
       </c>
       <c r="D483" t="b">
         <v>0</v>
@@ -7203,10 +7203,10 @@
         <v>0</v>
       </c>
       <c r="B484" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C484" t="n">
-        <v>15.34291581</v>
+        <v>50.29979466</v>
       </c>
       <c r="D484" t="b">
         <v>0</v>
@@ -7214,13 +7214,13 @@
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B485" t="n">
         <v>0</v>
       </c>
       <c r="C485" t="n">
-        <v>3.482546201</v>
+        <v>7.852156057</v>
       </c>
       <c r="D485" t="b">
         <v>0</v>
@@ -7231,38 +7231,38 @@
         <v>0</v>
       </c>
       <c r="B486" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C486" t="n">
-        <v>23.2936345</v>
+        <v>23.9835729</v>
       </c>
       <c r="D486" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B487" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C487" t="n">
-        <v>94.78439425000001</v>
+        <v>3.449691992</v>
       </c>
       <c r="D487" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B488" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C488" t="n">
-        <v>30.78439425</v>
+        <v>110.0287474</v>
       </c>
       <c r="D488" t="b">
         <v>0</v>
@@ -7273,10 +7273,10 @@
         <v>0</v>
       </c>
       <c r="B489" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C489" t="n">
-        <v>149.6180698</v>
+        <v>11.53182752</v>
       </c>
       <c r="D489" t="b">
         <v>0</v>
@@ -7290,7 +7290,7 @@
         <v>1</v>
       </c>
       <c r="C490" t="n">
-        <v>16.59137577</v>
+        <v>10.94045175</v>
       </c>
       <c r="D490" t="b">
         <v>1</v>
@@ -7301,10 +7301,10 @@
         <v>0</v>
       </c>
       <c r="B491" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C491" t="n">
-        <v>74.74332649</v>
+        <v>3.975359343</v>
       </c>
       <c r="D491" t="b">
         <v>1</v>
@@ -7318,7 +7318,7 @@
         <v>1</v>
       </c>
       <c r="C492" t="n">
-        <v>2.234086242</v>
+        <v>112.788501</v>
       </c>
       <c r="D492" t="b">
         <v>0</v>
@@ -7332,10 +7332,10 @@
         <v>1</v>
       </c>
       <c r="C493" t="n">
-        <v>20.04106776</v>
+        <v>8.772073922000001</v>
       </c>
       <c r="D493" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="494">
@@ -7343,10 +7343,10 @@
         <v>0</v>
       </c>
       <c r="B494" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C494" t="n">
-        <v>49.80698152</v>
+        <v>39.88501027</v>
       </c>
       <c r="D494" t="b">
         <v>0</v>
@@ -7357,24 +7357,24 @@
         <v>0</v>
       </c>
       <c r="B495" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C495" t="n">
-        <v>14.85010267</v>
+        <v>16.95277207</v>
       </c>
       <c r="D495" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B496" t="n">
         <v>1</v>
       </c>
       <c r="C496" t="n">
-        <v>39.22792608</v>
+        <v>3.975359343</v>
       </c>
       <c r="D496" t="b">
         <v>1</v>
@@ -7385,13 +7385,13 @@
         <v>0</v>
       </c>
       <c r="B497" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C497" t="n">
-        <v>11.89322382</v>
+        <v>14.45585216</v>
       </c>
       <c r="D497" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="498">
@@ -7402,10 +7402,10 @@
         <v>1</v>
       </c>
       <c r="C498" t="n">
-        <v>16.65708419</v>
+        <v>32.45995893</v>
       </c>
       <c r="D498" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="499">
@@ -7416,24 +7416,24 @@
         <v>1</v>
       </c>
       <c r="C499" t="n">
-        <v>82.75975359</v>
+        <v>10.7761807</v>
       </c>
       <c r="D499" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B500" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C500" t="n">
-        <v>55.95071869</v>
+        <v>26.0862423</v>
       </c>
       <c r="D500" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="501">
@@ -7441,24 +7441,24 @@
         <v>0</v>
       </c>
       <c r="B501" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C501" t="n">
-        <v>26.94045175</v>
+        <v>144.7556468</v>
       </c>
       <c r="D501" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="502">
       <c r="A502" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B502" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C502" t="n">
-        <v>12.32032854</v>
+        <v>10.02053388</v>
       </c>
       <c r="D502" t="b">
         <v>0</v>
@@ -7466,13 +7466,13 @@
     </row>
     <row r="503">
       <c r="A503" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B503" t="n">
         <v>0</v>
       </c>
       <c r="C503" t="n">
-        <v>16.95277207</v>
+        <v>123.6960986</v>
       </c>
       <c r="D503" t="b">
         <v>0</v>
@@ -7480,13 +7480,13 @@
     </row>
     <row r="504">
       <c r="A504" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B504" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C504" t="n">
-        <v>3.252566735</v>
+        <v>20.92813142</v>
       </c>
       <c r="D504" t="b">
         <v>1</v>
@@ -7500,7 +7500,7 @@
         <v>1</v>
       </c>
       <c r="C505" t="n">
-        <v>79.86858316</v>
+        <v>45.37166324</v>
       </c>
       <c r="D505" t="b">
         <v>1</v>
@@ -7514,7 +7514,7 @@
         <v>1</v>
       </c>
       <c r="C506" t="n">
-        <v>3.876796715</v>
+        <v>8.344969198999999</v>
       </c>
       <c r="D506" t="b">
         <v>0</v>
@@ -7522,13 +7522,13 @@
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B507" t="n">
         <v>0</v>
       </c>
       <c r="C507" t="n">
-        <v>19.35112936</v>
+        <v>14.48870637</v>
       </c>
       <c r="D507" t="b">
         <v>0</v>
@@ -7536,16 +7536,16 @@
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B508" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C508" t="n">
-        <v>54.01232033</v>
+        <v>33.67556468</v>
       </c>
       <c r="D508" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="509">
@@ -7553,10 +7553,10 @@
         <v>0</v>
       </c>
       <c r="B509" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C509" t="n">
-        <v>40.04928131</v>
+        <v>14.48870637</v>
       </c>
       <c r="D509" t="b">
         <v>0</v>
@@ -7564,13 +7564,13 @@
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B510" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C510" t="n">
-        <v>64.75564682</v>
+        <v>15.14579055</v>
       </c>
       <c r="D510" t="b">
         <v>0</v>
@@ -7581,24 +7581,24 @@
         <v>0</v>
       </c>
       <c r="B511" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C511" t="n">
-        <v>32.88706366</v>
+        <v>33.93839836</v>
       </c>
       <c r="D511" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B512" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C512" t="n">
-        <v>3.121149897</v>
+        <v>33.28131417</v>
       </c>
       <c r="D512" t="b">
         <v>0</v>
@@ -7606,16 +7606,16 @@
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B513" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C513" t="n">
-        <v>116.7310062</v>
+        <v>16.65708419</v>
       </c>
       <c r="D513" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="514">
@@ -7623,10 +7623,10 @@
         <v>0</v>
       </c>
       <c r="B514" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C514" t="n">
-        <v>13.01026694</v>
+        <v>22.73511294</v>
       </c>
       <c r="D514" t="b">
         <v>1</v>
@@ -7637,10 +7637,10 @@
         <v>0</v>
       </c>
       <c r="B515" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C515" t="n">
-        <v>70.30800821</v>
+        <v>12.8788501</v>
       </c>
       <c r="D515" t="b">
         <v>1</v>
@@ -7654,7 +7654,7 @@
         <v>0</v>
       </c>
       <c r="C516" t="n">
-        <v>12.64887064</v>
+        <v>27.56468172</v>
       </c>
       <c r="D516" t="b">
         <v>0</v>
@@ -7668,7 +7668,7 @@
         <v>1</v>
       </c>
       <c r="C517" t="n">
-        <v>25.36344969</v>
+        <v>42.57905544</v>
       </c>
       <c r="D517" t="b">
         <v>0</v>
@@ -7676,16 +7676,16 @@
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B518" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C518" t="n">
-        <v>42.38193018</v>
+        <v>22.24229979</v>
       </c>
       <c r="D518" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="519">
@@ -7693,10 +7693,10 @@
         <v>0</v>
       </c>
       <c r="B519" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C519" t="n">
-        <v>31.34291581</v>
+        <v>4.501026694</v>
       </c>
       <c r="D519" t="b">
         <v>0</v>
@@ -7704,13 +7704,13 @@
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B520" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C520" t="n">
-        <v>12.35318275</v>
+        <v>12.78028747</v>
       </c>
       <c r="D520" t="b">
         <v>1</v>
@@ -7724,7 +7724,7 @@
         <v>1</v>
       </c>
       <c r="C521" t="n">
-        <v>26.31622177</v>
+        <v>79.86858316</v>
       </c>
       <c r="D521" t="b">
         <v>1</v>
@@ -7732,41 +7732,41 @@
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B522" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C522" t="n">
-        <v>25.42915811</v>
+        <v>14.06160164</v>
       </c>
       <c r="D522" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B523" t="n">
         <v>0</v>
       </c>
       <c r="C523" t="n">
-        <v>23.6550308</v>
+        <v>16.95277207</v>
       </c>
       <c r="D523" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B524" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C524" t="n">
-        <v>0.755646817</v>
+        <v>5.026694045</v>
       </c>
       <c r="D524" t="b">
         <v>1</v>
@@ -7777,10 +7777,10 @@
         <v>0</v>
       </c>
       <c r="B525" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C525" t="n">
-        <v>48.6899384</v>
+        <v>19.74537988</v>
       </c>
       <c r="D525" t="b">
         <v>0</v>
@@ -7788,27 +7788,27 @@
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B526" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C526" t="n">
-        <v>70.83367556</v>
+        <v>48.19712526</v>
       </c>
       <c r="D526" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B527" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C527" t="n">
-        <v>40.3449692</v>
+        <v>10.61190965</v>
       </c>
       <c r="D527" t="b">
         <v>0</v>
@@ -7819,10 +7819,10 @@
         <v>0</v>
       </c>
       <c r="B528" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C528" t="n">
-        <v>82.82546201</v>
+        <v>31.96714579</v>
       </c>
       <c r="D528" t="b">
         <v>1</v>
@@ -7833,13 +7833,13 @@
         <v>0</v>
       </c>
       <c r="B529" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C529" t="n">
-        <v>11.99178645</v>
+        <v>132.8952772</v>
       </c>
       <c r="D529" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="530">
@@ -7850,7 +7850,7 @@
         <v>0</v>
       </c>
       <c r="C530" t="n">
-        <v>12.5174538</v>
+        <v>32.32854209</v>
       </c>
       <c r="D530" t="b">
         <v>0</v>
@@ -7864,7 +7864,7 @@
         <v>1</v>
       </c>
       <c r="C531" t="n">
-        <v>51.87679671</v>
+        <v>26.4476386</v>
       </c>
       <c r="D531" t="b">
         <v>1</v>
@@ -7872,16 +7872,16 @@
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B532" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C532" t="n">
-        <v>3.449691992</v>
+        <v>51.94250513</v>
       </c>
       <c r="D532" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="533">
@@ -7892,10 +7892,10 @@
         <v>1</v>
       </c>
       <c r="C533" t="n">
-        <v>27.36755647</v>
+        <v>44.97741273</v>
       </c>
       <c r="D533" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="534">
@@ -7906,10 +7906,10 @@
         <v>1</v>
       </c>
       <c r="C534" t="n">
-        <v>66.7926078</v>
+        <v>19.71252567</v>
       </c>
       <c r="D534" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="535">
@@ -7920,7 +7920,7 @@
         <v>1</v>
       </c>
       <c r="C535" t="n">
-        <v>19.18685832</v>
+        <v>4.073921971</v>
       </c>
       <c r="D535" t="b">
         <v>1</v>
@@ -7928,16 +7928,16 @@
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B536" t="n">
         <v>0</v>
       </c>
       <c r="C536" t="n">
-        <v>11.95893224</v>
+        <v>7.162217659</v>
       </c>
       <c r="D536" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="537">
@@ -7948,10 +7948,10 @@
         <v>0</v>
       </c>
       <c r="C537" t="n">
-        <v>53.42094456</v>
+        <v>26.21765914</v>
       </c>
       <c r="D537" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="538">
@@ -7962,10 +7962,10 @@
         <v>1</v>
       </c>
       <c r="C538" t="n">
-        <v>24.47638604</v>
+        <v>11.49897331</v>
       </c>
       <c r="D538" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="539">
@@ -7973,13 +7973,13 @@
         <v>0</v>
       </c>
       <c r="B539" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C539" t="n">
-        <v>44.94455852</v>
+        <v>17.41273101</v>
       </c>
       <c r="D539" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="540">
@@ -7987,13 +7987,13 @@
         <v>0</v>
       </c>
       <c r="B540" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C540" t="n">
-        <v>22.57084189</v>
+        <v>16.85420945</v>
       </c>
       <c r="D540" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="541">
@@ -8001,10 +8001,10 @@
         <v>0</v>
       </c>
       <c r="B541" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C541" t="n">
-        <v>13.8973306</v>
+        <v>43.92607803</v>
       </c>
       <c r="D541" t="b">
         <v>1</v>
@@ -8012,13 +8012,13 @@
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B542" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C542" t="n">
-        <v>89.19917864</v>
+        <v>14.6201232</v>
       </c>
       <c r="D542" t="b">
         <v>1</v>
@@ -8029,13 +8029,13 @@
         <v>0</v>
       </c>
       <c r="B543" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C543" t="n">
-        <v>48.45995893</v>
+        <v>27.23613963</v>
       </c>
       <c r="D543" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="544">
@@ -8043,13 +8043,13 @@
         <v>0</v>
       </c>
       <c r="B544" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C544" t="n">
-        <v>22.70225873</v>
+        <v>6.176591376</v>
       </c>
       <c r="D544" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="545">
@@ -8060,10 +8060,10 @@
         <v>1</v>
       </c>
       <c r="C545" t="n">
-        <v>96.52566735000001</v>
+        <v>11.72895277</v>
       </c>
       <c r="D545" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="546">
@@ -8071,13 +8071,13 @@
         <v>0</v>
       </c>
       <c r="B546" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C546" t="n">
-        <v>8.31211499</v>
+        <v>92.64887064</v>
       </c>
       <c r="D546" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="547">
@@ -8085,13 +8085,13 @@
         <v>0</v>
       </c>
       <c r="B547" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C547" t="n">
-        <v>144.5913758</v>
+        <v>132.8952772</v>
       </c>
       <c r="D547" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="548">
@@ -8102,21 +8102,21 @@
         <v>1</v>
       </c>
       <c r="C548" t="n">
-        <v>59.40041068</v>
+        <v>74.05338809</v>
       </c>
       <c r="D548" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B549" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C549" t="n">
-        <v>7.589322382</v>
+        <v>60.25462012</v>
       </c>
       <c r="D549" t="b">
         <v>1</v>
@@ -8124,16 +8124,16 @@
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B550" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C550" t="n">
-        <v>9.790554415000001</v>
+        <v>34.59548255</v>
       </c>
       <c r="D550" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="551">
@@ -8141,10 +8141,10 @@
         <v>0</v>
       </c>
       <c r="B551" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C551" t="n">
-        <v>43.4661191</v>
+        <v>7.030800821</v>
       </c>
       <c r="D551" t="b">
         <v>1</v>
@@ -8152,13 +8152,13 @@
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B552" t="n">
         <v>0</v>
       </c>
       <c r="C552" t="n">
-        <v>24.83778234</v>
+        <v>80.98562628000001</v>
       </c>
       <c r="D552" t="b">
         <v>1</v>
@@ -8172,7 +8172,7 @@
         <v>1</v>
       </c>
       <c r="C553" t="n">
-        <v>9.527720738999999</v>
+        <v>19.58110883</v>
       </c>
       <c r="D553" t="b">
         <v>1</v>
@@ -8180,13 +8180,13 @@
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B554" t="n">
         <v>0</v>
       </c>
       <c r="C554" t="n">
-        <v>45.30595483</v>
+        <v>7.589322382</v>
       </c>
       <c r="D554" t="b">
         <v>1</v>
@@ -8197,24 +8197,24 @@
         <v>0</v>
       </c>
       <c r="B555" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C555" t="n">
-        <v>11.03901437</v>
+        <v>93.8973306</v>
       </c>
       <c r="D555" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B556" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C556" t="n">
-        <v>61.79876797</v>
+        <v>17.01848049</v>
       </c>
       <c r="D556" t="b">
         <v>1</v>
@@ -8222,16 +8222,16 @@
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B557" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C557" t="n">
-        <v>21.88090349</v>
+        <v>15.34291581</v>
       </c>
       <c r="D557" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="558">
@@ -8239,27 +8239,27 @@
         <v>0</v>
       </c>
       <c r="B558" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C558" t="n">
-        <v>16.06570842</v>
+        <v>35.74537988</v>
       </c>
       <c r="D558" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B559" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C559" t="n">
-        <v>40.11498973</v>
+        <v>3.975359343</v>
       </c>
       <c r="D559" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="560">
@@ -8267,13 +8267,13 @@
         <v>0</v>
       </c>
       <c r="B560" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C560" t="n">
-        <v>113.8398357</v>
+        <v>26.21765914</v>
       </c>
       <c r="D560" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="561">
@@ -8281,13 +8281,13 @@
         <v>0</v>
       </c>
       <c r="B561" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C561" t="n">
-        <v>9.889117043000001</v>
+        <v>57.62628337</v>
       </c>
       <c r="D561" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="562">
@@ -8298,10 +8298,10 @@
         <v>1</v>
       </c>
       <c r="C562" t="n">
-        <v>8.180698152</v>
+        <v>129.2813142</v>
       </c>
       <c r="D562" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="563">
@@ -8312,21 +8312,21 @@
         <v>1</v>
       </c>
       <c r="C563" t="n">
-        <v>5.749486653</v>
+        <v>4.993839836</v>
       </c>
       <c r="D563" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B564" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C564" t="n">
-        <v>5.453798768</v>
+        <v>24.27926078</v>
       </c>
       <c r="D564" t="b">
         <v>0</v>
@@ -8334,16 +8334,16 @@
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B565" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C565" t="n">
-        <v>19.44969199</v>
+        <v>67.84394251000001</v>
       </c>
       <c r="D565" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="566">
@@ -8354,7 +8354,7 @@
         <v>1</v>
       </c>
       <c r="C566" t="n">
-        <v>19.44969199</v>
+        <v>58.21765914</v>
       </c>
       <c r="D566" t="b">
         <v>0</v>
@@ -8365,13 +8365,13 @@
         <v>0</v>
       </c>
       <c r="B567" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C567" t="n">
-        <v>39.22792608</v>
+        <v>49.70841889</v>
       </c>
       <c r="D567" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="568">
@@ -8382,7 +8382,7 @@
         <v>1</v>
       </c>
       <c r="C568" t="n">
-        <v>27.40041068</v>
+        <v>8.410677617999999</v>
       </c>
       <c r="D568" t="b">
         <v>0</v>
@@ -8396,24 +8396,24 @@
         <v>1</v>
       </c>
       <c r="C569" t="n">
-        <v>55.12936345</v>
+        <v>20.56673511</v>
       </c>
       <c r="D569" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B570" t="n">
         <v>0</v>
       </c>
       <c r="C570" t="n">
-        <v>47.6386037</v>
+        <v>24.3449692</v>
       </c>
       <c r="D570" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="571">
@@ -8424,7 +8424,7 @@
         <v>0</v>
       </c>
       <c r="C571" t="n">
-        <v>73.39630390000001</v>
+        <v>21.15811088</v>
       </c>
       <c r="D571" t="b">
         <v>0</v>
@@ -8438,7 +8438,7 @@
         <v>1</v>
       </c>
       <c r="C572" t="n">
-        <v>58.97330595</v>
+        <v>23.45790554</v>
       </c>
       <c r="D572" t="b">
         <v>0</v>
@@ -8452,38 +8452,38 @@
         <v>1</v>
       </c>
       <c r="C573" t="n">
-        <v>35.38398357</v>
+        <v>35.84394251</v>
       </c>
       <c r="D573" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B574" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C574" t="n">
-        <v>42.48049281</v>
+        <v>16.49281314</v>
       </c>
       <c r="D574" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B575" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C575" t="n">
-        <v>5.092402464</v>
+        <v>34.03696099</v>
       </c>
       <c r="D575" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="576">
@@ -8491,10 +8491,10 @@
         <v>0</v>
       </c>
       <c r="B576" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C576" t="n">
-        <v>20.76386037</v>
+        <v>34.49691992</v>
       </c>
       <c r="D576" t="b">
         <v>0</v>
@@ -8508,7 +8508,7 @@
         <v>0</v>
       </c>
       <c r="C577" t="n">
-        <v>26.15195072</v>
+        <v>22.73511294</v>
       </c>
       <c r="D577" t="b">
         <v>1</v>
@@ -8519,13 +8519,13 @@
         <v>0</v>
       </c>
       <c r="B578" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C578" t="n">
-        <v>12.68172485</v>
+        <v>81.64271047</v>
       </c>
       <c r="D578" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="579">
@@ -8533,10 +8533,10 @@
         <v>0</v>
       </c>
       <c r="B579" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C579" t="n">
-        <v>37.32238193</v>
+        <v>128.1314168</v>
       </c>
       <c r="D579" t="b">
         <v>0</v>
@@ -8544,16 +8544,16 @@
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B580" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C580" t="n">
-        <v>51.08829569</v>
+        <v>7.162217659</v>
       </c>
       <c r="D580" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="581">
@@ -8564,7 +8564,7 @@
         <v>1</v>
       </c>
       <c r="C581" t="n">
-        <v>12.38603696</v>
+        <v>115.5482546</v>
       </c>
       <c r="D581" t="b">
         <v>0</v>
@@ -8572,16 +8572,16 @@
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B582" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C582" t="n">
-        <v>30.68583162</v>
+        <v>17.60985626</v>
       </c>
       <c r="D582" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="583">
@@ -8589,27 +8589,27 @@
         <v>0</v>
       </c>
       <c r="B583" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C583" t="n">
-        <v>166.0780287</v>
+        <v>6.800821355</v>
       </c>
       <c r="D583" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B584" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C584" t="n">
-        <v>2.266940452</v>
+        <v>42.18480493</v>
       </c>
       <c r="D584" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="585">
@@ -8620,10 +8620,10 @@
         <v>1</v>
       </c>
       <c r="C585" t="n">
-        <v>21.48665298</v>
+        <v>28.15605749</v>
       </c>
       <c r="D585" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="586">
@@ -8634,24 +8634,24 @@
         <v>0</v>
       </c>
       <c r="C586" t="n">
-        <v>80.06570842000001</v>
+        <v>51.58110883</v>
       </c>
       <c r="D586" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B587" t="n">
         <v>0</v>
       </c>
       <c r="C587" t="n">
-        <v>52.66529774</v>
+        <v>3.811088296</v>
       </c>
       <c r="D587" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="588">
@@ -8662,10 +8662,10 @@
         <v>1</v>
       </c>
       <c r="C588" t="n">
-        <v>48.45995893</v>
+        <v>5.848049281</v>
       </c>
       <c r="D588" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="589">
@@ -8676,21 +8676,21 @@
         <v>0</v>
       </c>
       <c r="C589" t="n">
-        <v>18.49691992</v>
+        <v>15.60574949</v>
       </c>
       <c r="D589" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B590" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C590" t="n">
-        <v>21.88090349</v>
+        <v>19.05544148</v>
       </c>
       <c r="D590" t="b">
         <v>0</v>
@@ -8701,10 +8701,10 @@
         <v>0</v>
       </c>
       <c r="B591" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C591" t="n">
-        <v>1.839835729</v>
+        <v>73.13347023</v>
       </c>
       <c r="D591" t="b">
         <v>0</v>
@@ -8718,7 +8718,7 @@
         <v>0</v>
       </c>
       <c r="C592" t="n">
-        <v>8.640657084000001</v>
+        <v>89.00205339</v>
       </c>
       <c r="D592" t="b">
         <v>1</v>
@@ -8726,16 +8726,16 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B593" t="n">
         <v>0</v>
       </c>
       <c r="C593" t="n">
-        <v>22.07802875</v>
+        <v>79.80287473999999</v>
       </c>
       <c r="D593" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="594">
@@ -8746,10 +8746,10 @@
         <v>1</v>
       </c>
       <c r="C594" t="n">
-        <v>13.07597536</v>
+        <v>10.51334702</v>
       </c>
       <c r="D594" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="595">
@@ -8757,10 +8757,10 @@
         <v>0</v>
       </c>
       <c r="B595" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C595" t="n">
-        <v>4.76386037</v>
+        <v>9.034907598</v>
       </c>
       <c r="D595" t="b">
         <v>0</v>
@@ -8774,7 +8774,7 @@
         <v>1</v>
       </c>
       <c r="C596" t="n">
-        <v>46.78439425</v>
+        <v>63.54004107</v>
       </c>
       <c r="D596" t="b">
         <v>1</v>
@@ -8788,7 +8788,7 @@
         <v>1</v>
       </c>
       <c r="C597" t="n">
-        <v>57.82340862</v>
+        <v>10.84188912</v>
       </c>
       <c r="D597" t="b">
         <v>1</v>
@@ -8802,7 +8802,7 @@
         <v>1</v>
       </c>
       <c r="C598" t="n">
-        <v>22.66940452</v>
+        <v>27.4661191</v>
       </c>
       <c r="D598" t="b">
         <v>0</v>
@@ -8810,30 +8810,30 @@
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B599" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C599" t="n">
-        <v>28.81314168</v>
+        <v>8.87063655</v>
       </c>
       <c r="D599" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B600" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C600" t="n">
-        <v>8.180698152</v>
+        <v>128.0657084</v>
       </c>
       <c r="D600" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="601">
@@ -8841,13 +8841,13 @@
         <v>0</v>
       </c>
       <c r="B601" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C601" t="n">
-        <v>96.72279261</v>
+        <v>32.88706366</v>
       </c>
       <c r="D601" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="602">
@@ -8858,21 +8858,21 @@
         <v>0</v>
       </c>
       <c r="C602" t="n">
-        <v>5.388090349</v>
+        <v>15.93429158</v>
       </c>
       <c r="D602" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B603" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C603" t="n">
-        <v>15.11293634</v>
+        <v>60.78028747</v>
       </c>
       <c r="D603" t="b">
         <v>0</v>
@@ -8880,13 +8880,13 @@
     </row>
     <row r="604">
       <c r="A604" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B604" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C604" t="n">
-        <v>81.83983573</v>
+        <v>5.650924025</v>
       </c>
       <c r="D604" t="b">
         <v>1</v>
@@ -8894,13 +8894,13 @@
     </row>
     <row r="605">
       <c r="A605" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B605" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C605" t="n">
-        <v>33.57700205</v>
+        <v>9.790554415000001</v>
       </c>
       <c r="D605" t="b">
         <v>1</v>
@@ -8914,10 +8914,10 @@
         <v>1</v>
       </c>
       <c r="C606" t="n">
-        <v>6.143737166</v>
+        <v>18.7926078</v>
       </c>
       <c r="D606" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="607">
@@ -8928,10 +8928,10 @@
         <v>1</v>
       </c>
       <c r="C607" t="n">
-        <v>133.9137577</v>
+        <v>36.73100616</v>
       </c>
       <c r="D607" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="608">
@@ -8942,7 +8942,7 @@
         <v>1</v>
       </c>
       <c r="C608" t="n">
-        <v>52.50102669</v>
+        <v>13.17453799</v>
       </c>
       <c r="D608" t="b">
         <v>1</v>
@@ -8956,7 +8956,7 @@
         <v>1</v>
       </c>
       <c r="C609" t="n">
-        <v>31.50718686</v>
+        <v>94.12731006</v>
       </c>
       <c r="D609" t="b">
         <v>0</v>
@@ -8964,27 +8964,27 @@
     </row>
     <row r="610">
       <c r="A610" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B610" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C610" t="n">
-        <v>11.69609856</v>
+        <v>27.56468172</v>
       </c>
       <c r="D610" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="611">
       <c r="A611" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B611" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C611" t="n">
-        <v>37.12525667</v>
+        <v>53.19096509</v>
       </c>
       <c r="D611" t="b">
         <v>1</v>
@@ -8992,13 +8992,13 @@
     </row>
     <row r="612">
       <c r="A612" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B612" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C612" t="n">
-        <v>6.866529774</v>
+        <v>1.80698152</v>
       </c>
       <c r="D612" t="b">
         <v>0</v>
@@ -9009,41 +9009,41 @@
         <v>0</v>
       </c>
       <c r="B613" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C613" t="n">
-        <v>29.01026694</v>
+        <v>18.56262834</v>
       </c>
       <c r="D613" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="614">
       <c r="A614" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B614" t="n">
         <v>1</v>
       </c>
       <c r="C614" t="n">
-        <v>16.75564682</v>
+        <v>3.416837782</v>
       </c>
       <c r="D614" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="615">
       <c r="A615" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B615" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C615" t="n">
-        <v>73.82340862</v>
+        <v>26.94045175</v>
       </c>
       <c r="D615" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="616">
@@ -9054,7 +9054,7 @@
         <v>1</v>
       </c>
       <c r="C616" t="n">
-        <v>57.52772074</v>
+        <v>45.07597536</v>
       </c>
       <c r="D616" t="b">
         <v>0</v>
@@ -9068,10 +9068,10 @@
         <v>0</v>
       </c>
       <c r="C617" t="n">
-        <v>64.29568789</v>
+        <v>49.7412731</v>
       </c>
       <c r="D617" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="618">
@@ -9082,10 +9082,10 @@
         <v>1</v>
       </c>
       <c r="C618" t="n">
-        <v>7.162217659</v>
+        <v>4.960985626</v>
       </c>
       <c r="D618" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="619">
@@ -9096,7 +9096,7 @@
         <v>1</v>
       </c>
       <c r="C619" t="n">
-        <v>23.68788501</v>
+        <v>41.69199179</v>
       </c>
       <c r="D619" t="b">
         <v>1</v>
@@ -9107,10 +9107,10 @@
         <v>0</v>
       </c>
       <c r="B620" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C620" t="n">
-        <v>45.5687885</v>
+        <v>54.07802875</v>
       </c>
       <c r="D620" t="b">
         <v>1</v>
@@ -9121,13 +9121,13 @@
         <v>0</v>
       </c>
       <c r="B621" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C621" t="n">
-        <v>13.66735113</v>
+        <v>0.492813142</v>
       </c>
       <c r="D621" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="622">
@@ -9138,10 +9138,10 @@
         <v>1</v>
       </c>
       <c r="C622" t="n">
-        <v>51.08829569</v>
+        <v>26.67761807</v>
       </c>
       <c r="D622" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="623">
@@ -9149,13 +9149,13 @@
         <v>0</v>
       </c>
       <c r="B623" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C623" t="n">
-        <v>140.2217659</v>
+        <v>25.98767967</v>
       </c>
       <c r="D623" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="624">
@@ -9166,7 +9166,7 @@
         <v>1</v>
       </c>
       <c r="C624" t="n">
-        <v>0.492813142</v>
+        <v>3.121149897</v>
       </c>
       <c r="D624" t="b">
         <v>0</v>
@@ -9177,13 +9177,13 @@
         <v>0</v>
       </c>
       <c r="B625" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C625" t="n">
-        <v>47.96714579</v>
+        <v>6.078028747</v>
       </c>
       <c r="D625" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="626">
@@ -9191,24 +9191,24 @@
         <v>0</v>
       </c>
       <c r="B626" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C626" t="n">
-        <v>55.78644764</v>
+        <v>11.79466119</v>
       </c>
       <c r="D626" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="627">
       <c r="A627" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B627" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C627" t="n">
-        <v>38.89938398</v>
+        <v>7.852156057</v>
       </c>
       <c r="D627" t="b">
         <v>0</v>
@@ -9222,7 +9222,7 @@
         <v>1</v>
       </c>
       <c r="C628" t="n">
-        <v>114.8583162</v>
+        <v>8.607802875000001</v>
       </c>
       <c r="D628" t="b">
         <v>1</v>
@@ -9236,7 +9236,7 @@
         <v>0</v>
       </c>
       <c r="C629" t="n">
-        <v>26.11909651</v>
+        <v>12.78028747</v>
       </c>
       <c r="D629" t="b">
         <v>1</v>
@@ -9247,10 +9247,10 @@
         <v>0</v>
       </c>
       <c r="B630" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C630" t="n">
-        <v>87.68788501</v>
+        <v>22.73511294</v>
       </c>
       <c r="D630" t="b">
         <v>1</v>
@@ -9261,10 +9261,10 @@
         <v>0</v>
       </c>
       <c r="B631" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C631" t="n">
-        <v>42.61190965</v>
+        <v>1.347022587</v>
       </c>
       <c r="D631" t="b">
         <v>0</v>
@@ -9278,7 +9278,7 @@
         <v>1</v>
       </c>
       <c r="C632" t="n">
-        <v>5.289527721</v>
+        <v>2.39835729</v>
       </c>
       <c r="D632" t="b">
         <v>0</v>
@@ -9292,10 +9292,10 @@
         <v>1</v>
       </c>
       <c r="C633" t="n">
-        <v>94.78439425000001</v>
+        <v>15.14579055</v>
       </c>
       <c r="D633" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="634">
@@ -9303,10 +9303,10 @@
         <v>0</v>
       </c>
       <c r="B634" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C634" t="n">
-        <v>86.83367556</v>
+        <v>23.9835729</v>
       </c>
       <c r="D634" t="b">
         <v>1</v>
@@ -9320,7 +9320,7 @@
         <v>1</v>
       </c>
       <c r="C635" t="n">
-        <v>2.792607803</v>
+        <v>23.95071869</v>
       </c>
       <c r="D635" t="b">
         <v>1</v>
@@ -9334,10 +9334,10 @@
         <v>1</v>
       </c>
       <c r="C636" t="n">
-        <v>13.33880903</v>
+        <v>13.73305955</v>
       </c>
       <c r="D636" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="637">
@@ -9348,7 +9348,7 @@
         <v>1</v>
       </c>
       <c r="C637" t="n">
-        <v>16.65708419</v>
+        <v>33.57700205</v>
       </c>
       <c r="D637" t="b">
         <v>0</v>
@@ -9362,7 +9362,7 @@
         <v>1</v>
       </c>
       <c r="C638" t="n">
-        <v>12.02464066</v>
+        <v>34.56262834</v>
       </c>
       <c r="D638" t="b">
         <v>1</v>
@@ -9376,10 +9376,10 @@
         <v>1</v>
       </c>
       <c r="C639" t="n">
-        <v>8.936344969</v>
+        <v>7.12936345</v>
       </c>
       <c r="D639" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="640">
@@ -9387,13 +9387,13 @@
         <v>0</v>
       </c>
       <c r="B640" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C640" t="n">
-        <v>23.52361396</v>
+        <v>70.93223819000001</v>
       </c>
       <c r="D640" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="641">
@@ -9404,10 +9404,10 @@
         <v>1</v>
       </c>
       <c r="C641" t="n">
-        <v>18.16837782</v>
+        <v>123.0718686</v>
       </c>
       <c r="D641" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="642">
@@ -9418,10 +9418,10 @@
         <v>1</v>
       </c>
       <c r="C642" t="n">
-        <v>23.2936345</v>
+        <v>48.09856263</v>
       </c>
       <c r="D642" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="643">
@@ -9432,10 +9432,10 @@
         <v>1</v>
       </c>
       <c r="C643" t="n">
-        <v>23.45790554</v>
+        <v>44.48459959</v>
       </c>
       <c r="D643" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="644">
@@ -9446,7 +9446,7 @@
         <v>0</v>
       </c>
       <c r="C644" t="n">
-        <v>11.8275154</v>
+        <v>36.59958932</v>
       </c>
       <c r="D644" t="b">
         <v>0</v>
@@ -9457,10 +9457,10 @@
         <v>0</v>
       </c>
       <c r="B645" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C645" t="n">
-        <v>45.37166324</v>
+        <v>12.05749487</v>
       </c>
       <c r="D645" t="b">
         <v>1</v>
@@ -9474,7 +9474,7 @@
         <v>1</v>
       </c>
       <c r="C646" t="n">
-        <v>63.70431211</v>
+        <v>103.5893224</v>
       </c>
       <c r="D646" t="b">
         <v>0</v>
@@ -9485,10 +9485,10 @@
         <v>0</v>
       </c>
       <c r="B647" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C647" t="n">
-        <v>30.35728953</v>
+        <v>82.7926078</v>
       </c>
       <c r="D647" t="b">
         <v>0</v>
@@ -9502,21 +9502,21 @@
         <v>1</v>
       </c>
       <c r="C648" t="n">
-        <v>8.180698152</v>
+        <v>101.5195072</v>
       </c>
       <c r="D648" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="649">
       <c r="A649" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B649" t="n">
         <v>0</v>
       </c>
       <c r="C649" t="n">
-        <v>95.96714579</v>
+        <v>11.56468172</v>
       </c>
       <c r="D649" t="b">
         <v>0</v>
@@ -9527,10 +9527,10 @@
         <v>1</v>
       </c>
       <c r="B650" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C650" t="n">
-        <v>48.19712526</v>
+        <v>7.950718686</v>
       </c>
       <c r="D650" t="b">
         <v>0</v>
@@ -9541,10 +9541,10 @@
         <v>0</v>
       </c>
       <c r="B651" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C651" t="n">
-        <v>24.27926078</v>
+        <v>46.9486653</v>
       </c>
       <c r="D651" t="b">
         <v>0</v>
@@ -9555,27 +9555,27 @@
         <v>0</v>
       </c>
       <c r="B652" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C652" t="n">
-        <v>26.21765914</v>
+        <v>65.37987680000001</v>
       </c>
       <c r="D652" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="653">
       <c r="A653" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B653" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C653" t="n">
-        <v>48.62422998</v>
+        <v>44.02464066</v>
       </c>
       <c r="D653" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="654">
@@ -9586,7 +9586,7 @@
         <v>0</v>
       </c>
       <c r="C654" t="n">
-        <v>15.17864476</v>
+        <v>12.25462012</v>
       </c>
       <c r="D654" t="b">
         <v>0</v>
@@ -9600,7 +9600,7 @@
         <v>1</v>
       </c>
       <c r="C655" t="n">
-        <v>109.2402464</v>
+        <v>39.68788501</v>
       </c>
       <c r="D655" t="b">
         <v>0</v>
@@ -9608,13 +9608,13 @@
     </row>
     <row r="656">
       <c r="A656" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B656" t="n">
         <v>1</v>
       </c>
       <c r="C656" t="n">
-        <v>132.4024641</v>
+        <v>50.23408624</v>
       </c>
       <c r="D656" t="b">
         <v>0</v>
@@ -9622,44 +9622,44 @@
     </row>
     <row r="657">
       <c r="A657" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B657" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C657" t="n">
-        <v>99.77823409</v>
+        <v>13.40451745</v>
       </c>
       <c r="D657" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="658">
       <c r="A658" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B658" t="n">
         <v>0</v>
       </c>
       <c r="C658" t="n">
-        <v>24.27926078</v>
+        <v>13.40451745</v>
       </c>
       <c r="D658" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="659">
       <c r="A659" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B659" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C659" t="n">
-        <v>10.48049281</v>
+        <v>9.067761807</v>
       </c>
       <c r="D659" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="660">
@@ -9670,7 +9670,7 @@
         <v>1</v>
       </c>
       <c r="C660" t="n">
-        <v>23.12936345</v>
+        <v>40.31211499</v>
       </c>
       <c r="D660" t="b">
         <v>0</v>
@@ -9684,10 +9684,10 @@
         <v>0</v>
       </c>
       <c r="C661" t="n">
-        <v>36.96098563</v>
+        <v>16.06570842</v>
       </c>
       <c r="D661" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="662">
@@ -9695,13 +9695,13 @@
         <v>0</v>
       </c>
       <c r="B662" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C662" t="n">
-        <v>42.0862423</v>
+        <v>38.86652977</v>
       </c>
       <c r="D662" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="663">
@@ -9712,7 +9712,7 @@
         <v>1</v>
       </c>
       <c r="C663" t="n">
-        <v>26.94045175</v>
+        <v>22.63655031</v>
       </c>
       <c r="D663" t="b">
         <v>1</v>
@@ -9720,44 +9720,44 @@
     </row>
     <row r="664">
       <c r="A664" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B664" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C664" t="n">
-        <v>9.330595483</v>
+        <v>9.199178645</v>
       </c>
       <c r="D664" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="665">
       <c r="A665" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B665" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C665" t="n">
-        <v>32.52566735</v>
+        <v>40.37782341</v>
       </c>
       <c r="D665" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="666">
       <c r="A666" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B666" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C666" t="n">
-        <v>4.041067762</v>
+        <v>42.38193018</v>
       </c>
       <c r="D666" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="667">
@@ -9765,10 +9765,10 @@
         <v>0</v>
       </c>
       <c r="B667" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C667" t="n">
-        <v>35.77823409</v>
+        <v>61.73305955</v>
       </c>
       <c r="D667" t="b">
         <v>1</v>
@@ -9776,16 +9776,16 @@
     </row>
     <row r="668">
       <c r="A668" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B668" t="n">
         <v>0</v>
       </c>
       <c r="C668" t="n">
-        <v>103.7207392</v>
+        <v>46.35728953</v>
       </c>
       <c r="D668" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="669">
@@ -9796,7 +9796,7 @@
         <v>1</v>
       </c>
       <c r="C669" t="n">
-        <v>34.95687885</v>
+        <v>3.975359343</v>
       </c>
       <c r="D669" t="b">
         <v>1</v>
@@ -9804,13 +9804,13 @@
     </row>
     <row r="670">
       <c r="A670" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B670" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C670" t="n">
-        <v>33.97125257</v>
+        <v>51.31827515</v>
       </c>
       <c r="D670" t="b">
         <v>0</v>
@@ -9818,27 +9818,27 @@
     </row>
     <row r="671">
       <c r="A671" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B671" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C671" t="n">
-        <v>52.862423</v>
+        <v>27.92607803</v>
       </c>
       <c r="D671" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="672">
       <c r="A672" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B672" t="n">
         <v>0</v>
       </c>
       <c r="C672" t="n">
-        <v>6.176591376</v>
+        <v>78.68583162</v>
       </c>
       <c r="D672" t="b">
         <v>1</v>
@@ -9849,10 +9849,10 @@
         <v>0</v>
       </c>
       <c r="B673" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="C673" t="n">
-        <v>53.09240246</v>
+        <v>61.07597536</v>
       </c>
       <c r="D673" t="b">
         <v>0</v>
@@ -9866,10 +9866,10 @@
         <v>0</v>
       </c>
       <c r="C674" t="n">
-        <v>103.3921971</v>
+        <v>79.54004107</v>
       </c>
       <c r="D674" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="675">
@@ -9880,10 +9880,10 @@
         <v>1</v>
       </c>
       <c r="C675" t="n">
-        <v>1.149897331</v>
+        <v>166.275154</v>
       </c>
       <c r="D675" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="676">
@@ -9894,7 +9894,7 @@
         <v>1</v>
       </c>
       <c r="C676" t="n">
-        <v>89.36344969</v>
+        <v>3.811088296</v>
       </c>
       <c r="D676" t="b">
         <v>1</v>
@@ -9902,16 +9902,16 @@
     </row>
     <row r="677">
       <c r="A677" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B677" t="n">
         <v>1</v>
       </c>
       <c r="C677" t="n">
-        <v>2.102669405</v>
+        <v>34.56262834</v>
       </c>
       <c r="D677" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="678">
@@ -9919,13 +9919,27 @@
         <v>0</v>
       </c>
       <c r="B678" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C678" t="n">
-        <v>118.8008214</v>
+        <v>68.27104722999999</v>
       </c>
       <c r="D678" t="b">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="679">
+      <c r="A679" t="n">
+        <v>1</v>
+      </c>
+      <c r="B679" t="n">
+        <v>0</v>
+      </c>
+      <c r="C679" t="n">
+        <v>5.420944559</v>
+      </c>
+      <c r="D679" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
